--- a/docs/WBS-ac-sm_IaC-Q3-2026.xlsx
+++ b/docs/WBS-ac-sm_IaC-Q3-2026.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Panduan" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">WBS!$A$4:$P$46</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">WBS!$A$4:$P$56</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,12 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="289">
   <si>
     <t xml:space="preserve">WBS - Port Loop Agentic GitHub Actions ke Repo HDL ac-sm_IaC</t>
   </si>
   <si>
-    <t xml:space="preserve">Periode kerja Triwulan III 2026 (Juli - Agustus - September) | Repo hargithub/ac-sm_IaC | WIB (UTC+07:00)  ||  Kolom Rencana = distribusi jadwal 3 bulan; kolom Aktual = tanggal yang benar-benar tercatat</t>
+    <t xml:space="preserve">Periode kerja Triwulan III 2026 | Repo hargithub/ac-sm_IaC | WIB (UTC+07:00) | Realisasi per 5 September 2026 pukul 19:00  ||  Kolom Rencana = distribusi jadwal 3 bulan; kolom Aktual = tanggal yang benar-benar tercatat</t>
   </si>
   <si>
     <t xml:space="preserve">WBS</t>
@@ -334,388 +334,490 @@
     <t xml:space="preserve">Buat GitHub App OCR baru</t>
   </si>
   <si>
+    <t xml:space="preserve">Terwujud sebagai opencodereview-ac-sm[bot]; slug memuat 'opencodereview' sesuai syarat dan nama LPMS-3 hilang. Bukti: secret OCR_GITHUB_APP_* 20 Agu 15:15 WIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Install App ke repo ac-sm_IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terkonfirmasi 5 Sep: step Get GitHub App Token sukses pada run ocr-review dan review terbit atas identitas App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isi 9 secret (9/9 terpasang)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/9 terpasang. 2 secret App 20 Agu; 7 sisanya 4 Sep 15:01-15:05; CODE_API_KEY dan PLAN_API_KEY 5 Sep saat model dipisah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verifikasi 9 secret dan slug bot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/9 secret terverifikasi; slug bot opencodereview-ac-sm memenuhi syarat pencocokan di 9 titik workflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Fondasi HDL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tulis CLAUDE.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit bf5e1d8, 161 baris: konvensi RTL, testbench, penamaan, alur agentic. Daftar fitur SystemVerilog diuji langsung ke Icarus 12, bukan disalin dokumentasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tetapkan struktur direktori dan build system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit bf5e1d8: rtl/, tb/, constr/, scripts/, Makefile, dua filelist, modul counter contoh dan testbench-nya. Lint dan sim diverifikasi lokal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issue #1 sebagai uji perdana loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skeleton dikerjakan langsung di 6.2; issue #1 dialihkan menjadi modul uart_tx agar sekaligus menguji loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Uji Loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tahap PLAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run 33944572063 sukses 1m55s. CATATAN: dijalankan agent-trigger versi lama; agent-plan.yml hasil pemisahan belum pernah jalan, lihat 9.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tahap IMPLEMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run 33961623295 sukses pada percobaan pertama; branch feat/acsm-issue-1 dan PR #2 terbentuk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review OpenCodeReview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 temuan inline terbit atas identitas opencodereview-ac-sm[bot], membuktikan App terpasang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agent-fix dan traceability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit c74d73c; kelima temuan dibalas per thread. Catatan: semua dilabeli Fixed padahal 4 di antaranya hanya menambah dokumentasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ac-verify dan auto-loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laporan terbit. Dengan thinker-model: 10 MET, 1 PARTIAL, 0 CANNOT VERIFY. Auto-trigger terbukti menyambung setelah token diganti ke GH_PAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ocr-rebuttal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belum teruji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 run: 17 skipped, 3 cancelled, 0 sukses. Hanya menyala bila agent-fix membantah dengan penanda Rebuttal, sedangkan kelima temuan dilabeli Fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop-breaker sampai label needs-human</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cap 3 putaran tercapai pada run 11:17:20. Eskalasinya sempat gagal karena gh tanpa --repo, sudah diperbaiki di 9.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 Perluasan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workflow CI bernama 'CI/CD Pipeline'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opsional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lint Verilator, elaborate GHDL, jalankan testbench; mengaktifkan trigger workflow_run dorman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dependency-review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relevan bila memakai dependensi pihak ketiga seperti core FuseSoC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runner self-hosted untuk simulasi berat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lpms-vm-runner terdaftar hanya ke LPMS-3; salah pasang membuat job menggantung di antrean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch protection pada main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gate ac-verify sudah menangani status BLOCKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Pengerasan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pisahkan tahap rencana ke agent-plan.yml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit d298d52. Dua tahap kini memakai model berbeda; prompt perencana mewajibkan 11 bagian dan menolak rencana di bawah 1.500 karakter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konfigurasi model lewat repository variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit 5c89658, e2a4926, 42a0c4e. Seluruh fallback dihapus agar salah konfigurasi terlihat, bukan tertutup diam-diam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming log, batas waktu percobaan, preflight gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit bb194ae. Menutup cacat bawaan LPMS-3: loop retry tidak pernah menyala saat agent menggantung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selaraskan preflight dengan konfigurasi tanpa fallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit 8e36aff. Preflight kini menguji nilai yang persis sama dengan step agent, plus gerbang konfigurasi kosong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seragamkan token agent-fix ke CODE_API_KEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit ab0f8bb. Pembagian token jadi konsisten: agent-plan pakai PLAN_API_KEY, agent-trigger dan agent-fix pakai CODE_API_KEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perbaikan gateway Cloudflare 524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dikerjakan di sisi server, bukan repo. Respons model sebelumnya melampaui batas baca proxy 120 detik. Inilah yang membuka jalan PR #2 berhasil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laporkan penyebab kegagalan sebenarnya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit 74f59ad. Menggantikan tebakan likely rate limit yang keliru; membaca api_error_status langsung dari stream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empat cacat dari siklus penuh pertama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit d967bf2. Loop-breaker gagal eskalasi, auto-trigger tak menyambung, temuan terhitung dobel, model penilai di-hardcode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulihkan circuit breaker dan footer commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commit 83607a8. Perbaikan auto-trigger sempat mematikan cap 3 putaran; deteksi kini lewat penanda isi, bukan tipe akun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uji agent-plan.yml hasil pemisahan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 run. Rencana issue #1 dibuat agent-trigger versi lama; workflow perencana yang baru belum pernah dieksekusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bobot dibagi rata 1/42 per tugas. Ubah kolom L bila ingin bobot berbasis effort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jadwal Mingguan Triwulan III 2026 - Rencana vs Aktual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X = minggu sesuai rencana  |  A = minggu tempat pekerjaan benar-benar terjadi  |  Hijau = tugas selesai, tembaga = belum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senin -&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blok A menumpuk di W08 (paket 1-4, 18 Agu) dan W10 (paket 5-7 dan 9, 5 Sep). Paket 6 dan 7 selesai LEBIH AWAL dari rencananya - blok A muncul sebelum blok X.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rekapitulasi per Paket Kerja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seluruh angka dihitung ulang dari sheet WBS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paket Kerja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jml Tugas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waktu Jalan (jam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jenis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catatan Waktu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hanya tanggal yang terbukti; durasi tidak tercatat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 mnt terukur, 13:20-13:33 pada 18 Agu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 mnt 39 dtk terukur, 13:33:39-13:39:18 pada 18 Agu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 mnt 47 dtk terukur, 13:39:18-13:43:05 pada 18 Agu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sekitar 1 mnt terukur, 13:43:05-13:44:02 pada 18 Agu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tersebar 20 Agu sampai 5 Sep, tidak tercatat kontinu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satu commit bf5e1d8; rentangnya tidak terukur terpisah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elapsed 11:26-18:45 WIB. BERIRISAN dengan paket 9, jangan dijumlahkan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">di luar cakupan yang disepakati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elapsed 16:10-18:59 WIB, commit pertama ke terakhir. BERIRISAN dengan paket 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rekapitulasi per Bulan (berdasarkan Rencana Selesai)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fokus Bulan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prasyarat OCR/Quality Gate di LPMS-3, analisis sumber, dan mayoritas adaptasi workflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agu 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sisa adaptasi, validasi, deployment ke ac-sm_IaC, dan pembuatan GitHub App OCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kredensial, fondasi HDL, siklus agentic penuh pertama, dan sembilan commit pengerasan loop di luar rencana awal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panduan Pembacaan dan Pengisian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENCANA vs AKTUAL - BACA INI DULU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kolom Rencana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribusi jadwal sepanjang Juli-September 2026, disusun mengikuti urutan logis pekerjaan. Ini baseline pelaporan triwulan, bukan catatan waktu sebenarnya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kolom Aktual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanggal yang benar-benar tercatat. Paket 1 sampai 4 seluruhnya dieksekusi pada 18 Agustus 2026 dalam satu sesi 24 menit - itulah sebabnya blok A di sheet Jadwal menumpuk di W08.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenapa dipisah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menimpa kolom Aktual dengan tanggal rencana akan membuat dokumen ini bertentangan dengan bukti commit dan timestamp server GitHub. Keduanya disimpan berdampingan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varians</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sengaja tidak dihitung. Baseline di sini disusun setelah pekerjaan selesai, jadi selisih rencana-aktual tidak bermakna sebagai ukuran kinerja.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEL YANG BOLEH DIEDIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teks biru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sel isian: Rencana Mulai, Rencana Selesai, Aktual Mulai, Aktual Selesai, Bobot, Realisasi di sheet WBS, dan Waktu Jalan di sheet Rekap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teks hitam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rumus. Jangan ditimpa - akan menghitung ulang sendiri saat sel biru diubah.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Format tanggal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dd-mmm-yy, contoh 18-Agu-26. Isi sebagai tanggal, bukan teks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Format persen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simpan sebagai pecahan: ketik 100% atau 1, bukan angka 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOSAKATA STATUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sudah dikerjakan dan terbukti dari berkas, commit, atau timestamp server.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Menunggu</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimasi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nama wajib mengandung 'opencodereview'; izin Pull requests + Issues read/write, webhook mati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Install App ke repo ac-sm_IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tidak bisa lewat CLI: endpoint instalasi menolak classic PAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isi 9 secret (0/9 terpasang)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nilai tidak bisa disalin dari LPMS-3: secret GitHub write-only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verifikasi 9 secret dan slug bot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pastikan slug App mengandung 'opencodereview' sebelum uji coba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 Fondasi HDL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tulis CLAUDE.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konvensi penamaan, strategi reset, clock domain, build system, target device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tetapkan struktur direktori dan build system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rtl/, tb/, constr/ plus filelist .f atau Makefile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Issue #1 - skeleton repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Struktur, filelist, satu modul plus testbench self-checking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 Uji Loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tahap PLAN</t>
+    <t xml:space="preserve">Belum dikerjakan; menunggu tindakan pemilik akun.</t>
   </si>
   <si>
     <t xml:space="preserve">Terblokir</t>
   </si>
   <si>
-    <t xml:space="preserve">Komentar &lt;!-- agent-plan --&gt; dan label plan-posted; timeout 45 mnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tahap IMPLEMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branch feat/acsm-issue-N, lint, PR berlabel agent-generated; timeout 45 mnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review OpenCodeReview</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temuan inline di bawah identitas App; timeout 20 mnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agent-fix dan traceability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balasan Fixed/Rebuttal/Deferred per thread; timeout 35 mnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ac-verify dan auto-loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settle 45 dtk plus polling sampai agent-fix idle; timeout 10 mnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ocr-rebuttal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalur paling rapuh: bergantung penuh pada slug App, tanpa fallback marker body</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loop-breaker sampai label needs-human</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Butuh 3 siklus fix-review penuh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 Perluasan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workflow CI bernama 'CI/CD Pipeline'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opsional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lint Verilator, elaborate GHDL, jalankan testbench; mengaktifkan trigger workflow_run dorman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dependency-review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relevan bila memakai dependensi pihak ketiga seperti core FuseSoC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Runner self-hosted untuk simulasi berat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lpms-vm-runner terdaftar hanya ke LPMS-3; salah pasang membuat job menggantung di antrean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branch protection pada main</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gate ac-verify sudah menangani status BLOCKED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bobot dibagi rata 1/42 per tugas. Ubah kolom L bila ingin bobot berbasis effort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jadwal Mingguan Triwulan III 2026 - Rencana vs Aktual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X = minggu sesuai rencana  |  A = minggu tempat pekerjaan benar-benar terjadi  |  Hijau = tugas selesai, tembaga = belum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senin -&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rencana tersebar Jul-Sep sesuai urutan logis pekerjaan. Blok A menumpuk di W08 karena paket 1-4 benar-benar dieksekusi dalam satu hari, 18 Agu 2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rekapitulasi per Paket Kerja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seluruh angka dihitung ulang dari sheet WBS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paket Kerja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jml Tugas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waktu Jalan (jam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jenis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catatan Waktu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hanya tanggal yang terbukti; durasi tidak tercatat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 mnt terukur, 13:20-13:33 pada 18 Agu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 mnt 39 dtk terukur, 13:33:39-13:39:18 pada 18 Agu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 mnt 47 dtk terukur, 13:39:18-13:43:05 pada 18 Agu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sekitar 1 mnt terukur, 13:43:05-13:44:02 pada 18 Agu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 mnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turun ke 1 jam bila draf CLAUDE.md disiapkan agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mayoritas waktu tunggu mesin, bukan jam-orang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">di luar cakupan yang disepakati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rekapitulasi per Bulan (berdasarkan Rencana Selesai)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fokus Bulan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prasyarat OCR/Quality Gate di LPMS-3, analisis sumber, dan mayoritas adaptasi workflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agu 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sisa adaptasi, validasi, deployment ke ac-sm_IaC, dan awal penyiapan kredensial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sep 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kredensial rampung, fondasi repo HDL, uji loop end-to-end, dan perluasan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panduan Pembacaan dan Pengisian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RENCANA vs AKTUAL - BACA INI DULU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kolom Rencana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distribusi jadwal sepanjang Juli-September 2026, disusun mengikuti urutan logis pekerjaan. Ini baseline pelaporan triwulan, bukan catatan waktu sebenarnya.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kolom Aktual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tanggal yang benar-benar tercatat. Paket 1 sampai 4 seluruhnya dieksekusi pada 18 Agustus 2026 dalam satu sesi 24 menit - itulah sebabnya blok A di sheet Jadwal menumpuk di W08.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kenapa dipisah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menimpa kolom Aktual dengan tanggal rencana akan membuat dokumen ini bertentangan dengan bukti commit dan timestamp server GitHub. Keduanya disimpan berdampingan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varians</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sengaja tidak dihitung. Baseline di sini disusun setelah pekerjaan selesai, jadi selisih rencana-aktual tidak bermakna sebagai ukuran kinerja.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEL YANG BOLEH DIEDIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teks biru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sel isian: Rencana Mulai, Rencana Selesai, Aktual Mulai, Aktual Selesai, Bobot, Realisasi di sheet WBS, dan Waktu Jalan di sheet Rekap.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teks hitam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rumus. Jangan ditimpa - akan menghitung ulang sendiri saat sel biru diubah.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Format tanggal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dd-mmm-yy, contoh 18-Agu-26. Isi sebagai tanggal, bukan teks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Format persen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simpan sebagai pecahan: ketik 100% atau 1, bukan angka 100.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOSAKATA STATUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sudah dikerjakan dan terbukti dari berkas, commit, atau timestamp server.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belum dikerjakan; menunggu tindakan pemilik akun.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tidak dapat dimulai sebelum paket 5 tuntas.</t>
+    <t xml:space="preserve">Tidak dapat dimulai sebelum paket prasyaratnya tuntas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workflow-nya sudah terpasang dan aktif, tetapi jalurnya belum pernah benar-benar dieksekusi.</t>
   </si>
   <si>
     <t xml:space="preserve">Di luar cakupan yang disepakati; dicatat untuk fase berikutnya.</t>
@@ -736,10 +838,28 @@
     <t xml:space="preserve">mtime berkas, commit git 2026-08-18T13:43:05+07:00, dan timestamp server GitHub pushed_at 2026-08-18T06:43:11Z.</t>
   </si>
   <si>
-    <t xml:space="preserve">Paket 5-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimasi. Paket 7 diturunkan dari nilai nyata di workflow: timeout-minutes 45/35/20/10, stagger acak 0-120 detik, settle 45 detik plus polling maksimum 10 menit.</t>
+    <t xml:space="preserve">Paket 5 sampai 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aktual. Bukti: timestamp secret, waktu commit, dan waktu run GitHub Actions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paket 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimasi; belum dikerjakan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paket 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aktual, dari commit pertama ke terakhir. Paket ini TIDAK ada di rencana awal - lahir dari cacat yang terungkap saat siklus penuh pertama dijalankan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rentang beririsan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waktu jalan paket 7 dan paket 9 saling tumpang tindih karena dikerjakan berselang-seling. Jangan dijumlahkan.</t>
   </si>
   <si>
     <t xml:space="preserve">ASUMSI YANG DIPAKAI</t>
@@ -763,10 +883,10 @@
     <t xml:space="preserve">Dibagi rata 1/42 per tugas. Ubah kolom Bobot bila ingin bobot berbasis effort.</t>
   </si>
   <si>
-    <t xml:space="preserve">Jadwal Sep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mengikuti jalur kritis paket 5 - 6 - 7, paket 8 setelahnya. Belum dikonfirmasi ke kalender Anda.</t>
+    <t xml:space="preserve">Realisasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diperbarui 5 September 2026 pukul 19:00 WIB. Paket 5, 6, dan 7 selesai lebih awal dari baseline; paket 9 adalah penambahan cakupan di tengah triwulan.</t>
   </si>
   <si>
     <t xml:space="preserve">Waktu jalan</t>
@@ -789,7 +909,7 @@
     <numFmt numFmtId="170" formatCode="dd\-mmm"/>
     <numFmt numFmtId="171" formatCode="0.00"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -861,6 +981,14 @@
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FFA8541F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF79818F"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1012,7 +1140,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1097,6 +1225,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1105,31 +1241,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1137,15 +1273,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1169,7 +1305,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1177,15 +1317,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1198,7 +1334,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1234,6 +1370,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF2F6B4F"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF79818F"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1545,7 +1689,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -1660,14 +1804,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="11" t="n">
         <f aca="false">L5*M5</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O5" s="4" t="s">
         <v>23</v>
@@ -1713,14 +1857,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M6" s="18" t="n">
         <v>1</v>
       </c>
       <c r="N6" s="19" t="n">
         <f aca="false">L6*M6</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O6" s="12" t="s">
         <v>23</v>
@@ -1766,14 +1910,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="11" t="n">
         <f aca="false">L7*M7</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>23</v>
@@ -1819,14 +1963,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M8" s="18" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="19" t="n">
         <f aca="false">L8*M8</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O8" s="12" t="s">
         <v>23</v>
@@ -1872,14 +2016,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="11" t="n">
         <f aca="false">L9*M9</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O9" s="4" t="s">
         <v>23</v>
@@ -1925,14 +2069,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M10" s="18" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="19" t="n">
         <f aca="false">L10*M10</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O10" s="12" t="s">
         <v>23</v>
@@ -1978,14 +2122,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M11" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="11" t="n">
         <f aca="false">L11*M11</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>23</v>
@@ -2031,14 +2175,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L12" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M12" s="18" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="19" t="n">
         <f aca="false">L12*M12</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O12" s="12" t="s">
         <v>23</v>
@@ -2084,14 +2228,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M13" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="11" t="n">
         <f aca="false">L13*M13</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O13" s="4" t="s">
         <v>23</v>
@@ -2137,14 +2281,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L14" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M14" s="18" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="19" t="n">
         <f aca="false">L14*M14</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O14" s="12" t="s">
         <v>23</v>
@@ -2190,14 +2334,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M15" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="11" t="n">
         <f aca="false">L15*M15</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O15" s="4" t="s">
         <v>23</v>
@@ -2243,14 +2387,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L16" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="19" t="n">
         <f aca="false">L16*M16</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O16" s="12" t="s">
         <v>23</v>
@@ -2296,14 +2440,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M17" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="11" t="n">
         <f aca="false">L17*M17</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O17" s="4" t="s">
         <v>23</v>
@@ -2349,14 +2493,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L18" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M18" s="18" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="19" t="n">
         <f aca="false">L18*M18</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O18" s="12" t="s">
         <v>23</v>
@@ -2402,14 +2546,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M19" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="11" t="n">
         <f aca="false">L19*M19</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O19" s="4" t="s">
         <v>23</v>
@@ -2455,14 +2599,14 @@
         <v>Jul 2026</v>
       </c>
       <c r="L20" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M20" s="18" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="19" t="n">
         <f aca="false">L20*M20</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O20" s="12" t="s">
         <v>23</v>
@@ -2508,14 +2652,14 @@
         <v>Agu 2026</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M21" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="11" t="n">
         <f aca="false">L21*M21</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O21" s="4" t="s">
         <v>23</v>
@@ -2561,14 +2705,14 @@
         <v>Agu 2026</v>
       </c>
       <c r="L22" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M22" s="18" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="19" t="n">
         <f aca="false">L22*M22</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O22" s="12" t="s">
         <v>23</v>
@@ -2614,14 +2758,14 @@
         <v>Agu 2026</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M23" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="11" t="n">
         <f aca="false">L23*M23</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O23" s="4" t="s">
         <v>23</v>
@@ -2667,14 +2811,14 @@
         <v>Agu 2026</v>
       </c>
       <c r="L24" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M24" s="18" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="19" t="n">
         <f aca="false">L24*M24</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O24" s="12" t="s">
         <v>23</v>
@@ -2720,14 +2864,14 @@
         <v>Agu 2026</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M25" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="11" t="n">
         <f aca="false">L25*M25</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O25" s="4" t="s">
         <v>23</v>
@@ -2773,14 +2917,14 @@
         <v>Agu 2026</v>
       </c>
       <c r="L26" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M26" s="18" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="19" t="n">
         <f aca="false">L26*M26</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O26" s="12" t="s">
         <v>23</v>
@@ -2826,14 +2970,14 @@
         <v>Agu 2026</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M27" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="11" t="n">
         <f aca="false">L27*M27</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O27" s="4" t="s">
         <v>23</v>
@@ -2879,14 +3023,14 @@
         <v>Agu 2026</v>
       </c>
       <c r="L28" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M28" s="18" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="19" t="n">
         <f aca="false">L28*M28</f>
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O28" s="12" t="s">
         <v>23</v>
@@ -2895,7 +3039,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
         <v>99</v>
       </c>
@@ -2908,8 +3052,8 @@
       <c r="D29" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E29" s="20" t="s">
-        <v>102</v>
+      <c r="E29" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="F29" s="8" t="n">
         <v>46258</v>
@@ -2921,44 +3065,48 @@
         <f aca="false">NETWORKDAYS(F29,G29)</f>
         <v>3</v>
       </c>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
+      <c r="I29" s="8" t="n">
+        <v>46254</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>46254</v>
+      </c>
       <c r="K29" s="4" t="str">
         <f aca="false">IF(G29="","",CHOOSE(MONTH(G29),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G29))</f>
         <v>Agu 2026</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="11" t="n">
         <f aca="false">L29*M29</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="P29" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="s">
-        <v>105</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>100</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="21" t="s">
-        <v>102</v>
+      <c r="E30" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="F30" s="16" t="n">
         <v>46261</v>
@@ -2970,44 +3118,48 @@
         <f aca="false">NETWORKDAYS(F30,G30)</f>
         <v>1</v>
       </c>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
+      <c r="I30" s="16" t="n">
+        <v>46254</v>
+      </c>
+      <c r="J30" s="16" t="n">
+        <v>46270</v>
+      </c>
       <c r="K30" s="12" t="str">
         <f aca="false">IF(G30="","",CHOOSE(MONTH(G30),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G30))</f>
         <v>Agu 2026</v>
       </c>
       <c r="L30" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M30" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="19" t="n">
         <f aca="false">L30*M30</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="P30" s="14" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>100</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="20" t="s">
-        <v>102</v>
+      <c r="E31" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>46262</v>
@@ -3019,44 +3171,48 @@
         <f aca="false">NETWORKDAYS(F31,G31)</f>
         <v>4</v>
       </c>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
+      <c r="I31" s="8" t="n">
+        <v>46254</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>46270</v>
+      </c>
       <c r="K31" s="4" t="str">
         <f aca="false">IF(G31="","",CHOOSE(MONTH(G31),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G31))</f>
         <v>Sep 2026</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M31" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="11" t="n">
         <f aca="false">L31*M31</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>100</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E32" s="21" t="s">
-        <v>102</v>
+      <c r="E32" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="F32" s="16" t="n">
         <v>46268</v>
@@ -3068,44 +3224,48 @@
         <f aca="false">NETWORKDAYS(F32,G32)</f>
         <v>2</v>
       </c>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
+      <c r="I32" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J32" s="16" t="n">
+        <v>46270</v>
+      </c>
       <c r="K32" s="12" t="str">
         <f aca="false">IF(G32="","",CHOOSE(MONTH(G32),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G32))</f>
         <v>Sep 2026</v>
       </c>
       <c r="L32" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M32" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="19" t="n">
         <f aca="false">L32*M32</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O32" s="12" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="P32" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="C33" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E33" s="20" t="s">
-        <v>102</v>
+      <c r="E33" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>46272</v>
@@ -3117,44 +3277,48 @@
         <f aca="false">NETWORKDAYS(F33,G33)</f>
         <v>2</v>
       </c>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
+      <c r="I33" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>46270</v>
+      </c>
       <c r="K33" s="4" t="str">
         <f aca="false">IF(G33="","",CHOOSE(MONTH(G33),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G33))</f>
         <v>Sep 2026</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M33" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" s="11" t="n">
         <f aca="false">L33*M33</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="P33" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" s="14" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>119</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E34" s="21" t="s">
-        <v>102</v>
+      <c r="E34" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="F34" s="16" t="n">
         <v>46274</v>
@@ -3166,44 +3330,48 @@
         <f aca="false">NETWORKDAYS(F34,G34)</f>
         <v>2</v>
       </c>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
+      <c r="I34" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J34" s="16" t="n">
+        <v>46270</v>
+      </c>
       <c r="K34" s="12" t="str">
         <f aca="false">IF(G34="","",CHOOSE(MONTH(G34),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G34))</f>
         <v>Sep 2026</v>
       </c>
       <c r="L34" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M34" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="19" t="n">
         <f aca="false">L34*M34</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O34" s="12" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="P34" s="14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E35" s="20" t="s">
-        <v>102</v>
+      <c r="E35" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="F35" s="8" t="n">
         <v>46276</v>
@@ -3215,44 +3383,48 @@
         <f aca="false">NETWORKDAYS(F35,G35)</f>
         <v>1</v>
       </c>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
+      <c r="I35" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>46270</v>
+      </c>
       <c r="K35" s="4" t="str">
         <f aca="false">IF(G35="","",CHOOSE(MONTH(G35),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G35))</f>
         <v>Sep 2026</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M35" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="11" t="n">
         <f aca="false">L35*M35</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="P35" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="13" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12" t="s">
+      <c r="C36" s="14" t="s">
         <v>124</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>126</v>
       </c>
       <c r="D36" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="21" t="s">
-        <v>127</v>
+      <c r="E36" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="F36" s="16" t="n">
         <v>46279</v>
@@ -3264,44 +3436,48 @@
         <f aca="false">NETWORKDAYS(F36,G36)</f>
         <v>1</v>
       </c>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
+      <c r="I36" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J36" s="16" t="n">
+        <v>46270</v>
+      </c>
       <c r="K36" s="12" t="str">
         <f aca="false">IF(G36="","",CHOOSE(MONTH(G36),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G36))</f>
         <v>Sep 2026</v>
       </c>
       <c r="L36" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M36" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="19" t="n">
         <f aca="false">L36*M36</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O36" s="12" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="P36" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E37" s="20" t="s">
-        <v>127</v>
+      <c r="E37" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>46279</v>
@@ -3313,44 +3489,48 @@
         <f aca="false">NETWORKDAYS(F37,G37)</f>
         <v>2</v>
       </c>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
+      <c r="I37" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>46270</v>
+      </c>
       <c r="K37" s="4" t="str">
         <f aca="false">IF(G37="","",CHOOSE(MONTH(G37),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G37))</f>
         <v>Sep 2026</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" s="11" t="n">
         <f aca="false">L37*M37</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E38" s="21" t="s">
-        <v>127</v>
+      <c r="E38" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="F38" s="16" t="n">
         <v>46280</v>
@@ -3362,44 +3542,48 @@
         <f aca="false">NETWORKDAYS(F38,G38)</f>
         <v>1</v>
       </c>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
+      <c r="I38" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J38" s="16" t="n">
+        <v>46270</v>
+      </c>
       <c r="K38" s="12" t="str">
         <f aca="false">IF(G38="","",CHOOSE(MONTH(G38),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G38))</f>
         <v>Sep 2026</v>
       </c>
       <c r="L38" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M38" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" s="19" t="n">
         <f aca="false">L38*M38</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O38" s="12" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E39" s="20" t="s">
-        <v>127</v>
+      <c r="E39" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>46281</v>
@@ -3411,44 +3595,48 @@
         <f aca="false">NETWORKDAYS(F39,G39)</f>
         <v>1</v>
       </c>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
+      <c r="I39" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>46270</v>
+      </c>
       <c r="K39" s="4" t="str">
         <f aca="false">IF(G39="","",CHOOSE(MONTH(G39),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G39))</f>
         <v>Sep 2026</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" s="11" t="n">
         <f aca="false">L39*M39</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D40" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E40" s="21" t="s">
-        <v>127</v>
+      <c r="E40" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="F40" s="16" t="n">
         <v>46281</v>
@@ -3460,44 +3648,48 @@
         <f aca="false">NETWORKDAYS(F40,G40)</f>
         <v>1</v>
       </c>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
+      <c r="I40" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J40" s="16" t="n">
+        <v>46270</v>
+      </c>
       <c r="K40" s="12" t="str">
         <f aca="false">IF(G40="","",CHOOSE(MONTH(G40),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G40))</f>
         <v>Sep 2026</v>
       </c>
       <c r="L40" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M40" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" s="19" t="n">
         <f aca="false">L40*M40</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O40" s="12" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="P40" s="14" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>37</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="F41" s="8" t="n">
         <v>46282</v>
@@ -3516,7 +3708,7 @@
         <v>Sep 2026</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M41" s="10" t="n">
         <v>0</v>
@@ -3526,27 +3718,27 @@
         <v>0</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="P41" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="12" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="s">
+      <c r="B42" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>145</v>
       </c>
       <c r="D42" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E42" s="21" t="s">
-        <v>127</v>
+      <c r="E42" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="F42" s="16" t="n">
         <v>46282</v>
@@ -3558,44 +3750,48 @@
         <f aca="false">NETWORKDAYS(F42,G42)</f>
         <v>2</v>
       </c>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
+      <c r="I42" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J42" s="16" t="n">
+        <v>46270</v>
+      </c>
       <c r="K42" s="12" t="str">
         <f aca="false">IF(G42="","",CHOOSE(MONTH(G42),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G42))</f>
         <v>Sep 2026</v>
       </c>
       <c r="L42" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" s="19" t="n">
         <f aca="false">L42*M42</f>
-        <v>0</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="O42" s="12" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="P42" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E43" s="20" t="s">
-        <v>150</v>
+      <c r="E43" s="21" t="s">
+        <v>149</v>
       </c>
       <c r="F43" s="8" t="n">
         <v>46286</v>
@@ -3614,7 +3810,7 @@
         <v>Sep 2026</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M43" s="10" t="n">
         <v>0</v>
@@ -3624,27 +3820,27 @@
         <v>0</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44" s="14" t="s">
         <v>152</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>153</v>
       </c>
       <c r="D44" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="21" t="s">
-        <v>150</v>
+      <c r="E44" s="22" t="s">
+        <v>149</v>
       </c>
       <c r="F44" s="16" t="n">
         <v>46289</v>
@@ -3663,7 +3859,7 @@
         <v>Sep 2026</v>
       </c>
       <c r="L44" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M44" s="18" t="n">
         <v>0</v>
@@ -3673,27 +3869,27 @@
         <v>0</v>
       </c>
       <c r="O44" s="12" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="P44" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E45" s="20" t="s">
-        <v>150</v>
+      <c r="E45" s="21" t="s">
+        <v>149</v>
       </c>
       <c r="F45" s="8" t="n">
         <v>46289</v>
@@ -3712,7 +3908,7 @@
         <v>Sep 2026</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M45" s="10" t="n">
         <v>0</v>
@@ -3722,27 +3918,27 @@
         <v>0</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C46" s="14" t="s">
         <v>158</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>159</v>
       </c>
       <c r="D46" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E46" s="21" t="s">
-        <v>150</v>
+      <c r="E46" s="22" t="s">
+        <v>149</v>
       </c>
       <c r="F46" s="16" t="n">
         <v>46290</v>
@@ -3761,7 +3957,7 @@
         <v>Sep 2026</v>
       </c>
       <c r="L46" s="17" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0192307692307692</v>
       </c>
       <c r="M46" s="18" t="n">
         <v>0</v>
@@ -3771,45 +3967,571 @@
         <v>0</v>
       </c>
       <c r="O46" s="12" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="P46" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="22"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="23" t="s">
+      <c r="B47" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="24" t="n">
-        <f aca="false">SUM(H5:H46)</f>
-        <v>76</v>
-      </c>
-      <c r="I47" s="22"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="22"/>
-      <c r="L47" s="25" t="n">
-        <f aca="false">SUM(L5:L46)</f>
+      <c r="C47" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <f aca="false">NETWORKDAYS(F47,G47)</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="K47" s="4" t="str">
+        <f aca="false">IF(G47="","",CHOOSE(MONTH(G47),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G47))</f>
+        <v>Sep 2026</v>
+      </c>
+      <c r="L47" s="9" t="n">
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="M47" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M47" s="22"/>
-      <c r="N47" s="26" t="n">
-        <f aca="false">SUM(N5:N46)</f>
-        <v>0.571428571428572</v>
-      </c>
-      <c r="O47" s="22"/>
-      <c r="P47" s="27" t="s">
-        <v>162</v>
+      <c r="N47" s="11" t="n">
+        <f aca="false">L47*M47</f>
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G48" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="H48" s="12" t="n">
+        <f aca="false">NETWORKDAYS(F48,G48)</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J48" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="K48" s="12" t="str">
+        <f aca="false">IF(G48="","",CHOOSE(MONTH(G48),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G48))</f>
+        <v>Sep 2026</v>
+      </c>
+      <c r="L48" s="17" t="n">
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="M48" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="19" t="n">
+        <f aca="false">L48*M48</f>
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="O48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P48" s="14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <f aca="false">NETWORKDAYS(F49,G49)</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="K49" s="4" t="str">
+        <f aca="false">IF(G49="","",CHOOSE(MONTH(G49),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G49))</f>
+        <v>Sep 2026</v>
+      </c>
+      <c r="L49" s="9" t="n">
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="M49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="11" t="n">
+        <f aca="false">L49*M49</f>
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <f aca="false">NETWORKDAYS(F50,G50)</f>
+        <v>0</v>
+      </c>
+      <c r="I50" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J50" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="K50" s="12" t="str">
+        <f aca="false">IF(G50="","",CHOOSE(MONTH(G50),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G50))</f>
+        <v>Sep 2026</v>
+      </c>
+      <c r="L50" s="17" t="n">
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="M50" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="19" t="n">
+        <f aca="false">L50*M50</f>
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="O50" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P50" s="14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <f aca="false">NETWORKDAYS(F51,G51)</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="K51" s="4" t="str">
+        <f aca="false">IF(G51="","",CHOOSE(MONTH(G51),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G51))</f>
+        <v>Sep 2026</v>
+      </c>
+      <c r="L51" s="9" t="n">
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="M51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="11" t="n">
+        <f aca="false">L51*M51</f>
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F52" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G52" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <f aca="false">NETWORKDAYS(F52,G52)</f>
+        <v>0</v>
+      </c>
+      <c r="I52" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J52" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="K52" s="12" t="str">
+        <f aca="false">IF(G52="","",CHOOSE(MONTH(G52),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G52))</f>
+        <v>Sep 2026</v>
+      </c>
+      <c r="L52" s="17" t="n">
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="M52" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="19" t="n">
+        <f aca="false">L52*M52</f>
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="O52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P52" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <f aca="false">NETWORKDAYS(F53,G53)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="K53" s="4" t="str">
+        <f aca="false">IF(G53="","",CHOOSE(MONTH(G53),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G53))</f>
+        <v>Sep 2026</v>
+      </c>
+      <c r="L53" s="9" t="n">
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="M53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="11" t="n">
+        <f aca="false">L53*M53</f>
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G54" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <f aca="false">NETWORKDAYS(F54,G54)</f>
+        <v>0</v>
+      </c>
+      <c r="I54" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J54" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="K54" s="12" t="str">
+        <f aca="false">IF(G54="","",CHOOSE(MONTH(G54),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G54))</f>
+        <v>Sep 2026</v>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="M54" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="19" t="n">
+        <f aca="false">L54*M54</f>
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="O54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P54" s="14" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <f aca="false">NETWORKDAYS(F55,G55)</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="K55" s="4" t="str">
+        <f aca="false">IF(G55="","",CHOOSE(MONTH(G55),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G55))</f>
+        <v>Sep 2026</v>
+      </c>
+      <c r="L55" s="9" t="n">
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="M55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" s="11" t="n">
+        <f aca="false">L55*M55</f>
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="O55" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P55" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E56" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F56" s="16" t="n">
+        <v>46272</v>
+      </c>
+      <c r="G56" s="16" t="n">
+        <v>46272</v>
+      </c>
+      <c r="H56" s="12" t="n">
+        <f aca="false">NETWORKDAYS(F56,G56)</f>
+        <v>1</v>
+      </c>
+      <c r="I56" s="16"/>
+      <c r="J56" s="16"/>
+      <c r="K56" s="12" t="str">
+        <f aca="false">IF(G56="","",CHOOSE(MONTH(G56),"Jan","Feb","Mar","Apr","Mei","Jun","Jul","Agu","Sep","Okt","Nov","Des")&amp;" "&amp;YEAR(G56))</f>
+        <v>Sep 2026</v>
+      </c>
+      <c r="L56" s="17" t="n">
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="M56" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="19" t="n">
+        <f aca="false">L56*M56</f>
+        <v>0</v>
+      </c>
+      <c r="O56" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="P56" s="14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="24"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="26" t="n">
+        <f aca="false">SUM(H5:H56)</f>
+        <v>77</v>
+      </c>
+      <c r="I57" s="24"/>
+      <c r="J57" s="24"/>
+      <c r="K57" s="24"/>
+      <c r="L57" s="27" t="n">
+        <f aca="false">SUM(L5:L56)</f>
+        <v>1</v>
+      </c>
+      <c r="M57" s="24"/>
+      <c r="N57" s="28" t="n">
+        <f aca="false">SUM(N5:N56)</f>
+        <v>0.884615384615385</v>
+      </c>
+      <c r="O57" s="24"/>
+      <c r="P57" s="29" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P46"/>
+  <autoFilter ref="A4:P56"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3826,7 +4548,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -3837,112 +4559,112 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" s="29" t="n">
+      <c r="C3" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="31" t="n">
         <v>46202</v>
       </c>
-      <c r="E3" s="29" t="n">
+      <c r="E3" s="31" t="n">
         <v>46209</v>
       </c>
-      <c r="F3" s="29" t="n">
+      <c r="F3" s="31" t="n">
         <v>46216</v>
       </c>
-      <c r="G3" s="29" t="n">
+      <c r="G3" s="31" t="n">
         <v>46223</v>
       </c>
-      <c r="H3" s="29" t="n">
+      <c r="H3" s="31" t="n">
         <v>46230</v>
       </c>
-      <c r="I3" s="29" t="n">
+      <c r="I3" s="31" t="n">
         <v>46237</v>
       </c>
-      <c r="J3" s="29" t="n">
+      <c r="J3" s="31" t="n">
         <v>46244</v>
       </c>
-      <c r="K3" s="29" t="n">
+      <c r="K3" s="31" t="n">
         <v>46251</v>
       </c>
-      <c r="L3" s="29" t="n">
+      <c r="L3" s="31" t="n">
         <v>46258</v>
       </c>
-      <c r="M3" s="29" t="n">
+      <c r="M3" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="N3" s="29" t="n">
+      <c r="N3" s="31" t="n">
         <v>46272</v>
       </c>
-      <c r="O3" s="29" t="n">
+      <c r="O3" s="31" t="n">
         <v>46279</v>
       </c>
-      <c r="P3" s="29" t="n">
+      <c r="P3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="Q3" s="29" t="n">
+      <c r="Q3" s="31" t="n">
         <v>46293</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="I4" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="K4" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="L4" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="M4" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="N4" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="O4" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="P4" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q4" s="31" t="s">
-        <v>179</v>
+      <c r="D4" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="L4" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="N4" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="O4" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="P4" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q4" s="33" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5636,7 +6358,7 @@
       </c>
       <c r="C29" s="4" t="str">
         <f aca="false">WBS!E29</f>
-        <v>Menunggu</v>
+        <v>Selesai</v>
       </c>
       <c r="D29" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I29&lt;&gt;"",WBS!$I29&lt;=D$3+6,WBS!$J29&gt;=D$3),"A",IF(AND(WBS!$F29&lt;=D$3+6,WBS!$G29&gt;=D$3),"X",""))</f>
@@ -5668,7 +6390,7 @@
       </c>
       <c r="K29" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I29&lt;&gt;"",WBS!$I29&lt;=K$3+6,WBS!$J29&gt;=K$3),"A",IF(AND(WBS!$F29&lt;=K$3+6,WBS!$G29&gt;=K$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="L29" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I29&lt;&gt;"",WBS!$I29&lt;=L$3+6,WBS!$J29&gt;=L$3),"A",IF(AND(WBS!$F29&lt;=L$3+6,WBS!$G29&gt;=L$3),"X",""))</f>
@@ -5706,7 +6428,7 @@
       </c>
       <c r="C30" s="4" t="str">
         <f aca="false">WBS!E30</f>
-        <v>Menunggu</v>
+        <v>Selesai</v>
       </c>
       <c r="D30" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I30&lt;&gt;"",WBS!$I30&lt;=D$3+6,WBS!$J30&gt;=D$3),"A",IF(AND(WBS!$F30&lt;=D$3+6,WBS!$G30&gt;=D$3),"X",""))</f>
@@ -5738,15 +6460,15 @@
       </c>
       <c r="K30" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I30&lt;&gt;"",WBS!$I30&lt;=K$3+6,WBS!$J30&gt;=K$3),"A",IF(AND(WBS!$F30&lt;=K$3+6,WBS!$G30&gt;=K$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="L30" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I30&lt;&gt;"",WBS!$I30&lt;=L$3+6,WBS!$J30&gt;=L$3),"A",IF(AND(WBS!$F30&lt;=L$3+6,WBS!$G30&gt;=L$3),"X",""))</f>
-        <v>X</v>
+        <v>A</v>
       </c>
       <c r="M30" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I30&lt;&gt;"",WBS!$I30&lt;=M$3+6,WBS!$J30&gt;=M$3),"A",IF(AND(WBS!$F30&lt;=M$3+6,WBS!$G30&gt;=M$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="N30" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I30&lt;&gt;"",WBS!$I30&lt;=N$3+6,WBS!$J30&gt;=N$3),"A",IF(AND(WBS!$F30&lt;=N$3+6,WBS!$G30&gt;=N$3),"X",""))</f>
@@ -5772,11 +6494,11 @@
       </c>
       <c r="B31" s="5" t="str">
         <f aca="false">WBS!C31</f>
-        <v>Isi 9 secret (0/9 terpasang)</v>
+        <v>Isi 9 secret (9/9 terpasang)</v>
       </c>
       <c r="C31" s="4" t="str">
         <f aca="false">WBS!E31</f>
-        <v>Menunggu</v>
+        <v>Selesai</v>
       </c>
       <c r="D31" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I31&lt;&gt;"",WBS!$I31&lt;=D$3+6,WBS!$J31&gt;=D$3),"A",IF(AND(WBS!$F31&lt;=D$3+6,WBS!$G31&gt;=D$3),"X",""))</f>
@@ -5808,15 +6530,15 @@
       </c>
       <c r="K31" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I31&lt;&gt;"",WBS!$I31&lt;=K$3+6,WBS!$J31&gt;=K$3),"A",IF(AND(WBS!$F31&lt;=K$3+6,WBS!$G31&gt;=K$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="L31" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I31&lt;&gt;"",WBS!$I31&lt;=L$3+6,WBS!$J31&gt;=L$3),"A",IF(AND(WBS!$F31&lt;=L$3+6,WBS!$G31&gt;=L$3),"X",""))</f>
-        <v>X</v>
+        <v>A</v>
       </c>
       <c r="M31" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I31&lt;&gt;"",WBS!$I31&lt;=M$3+6,WBS!$J31&gt;=M$3),"A",IF(AND(WBS!$F31&lt;=M$3+6,WBS!$G31&gt;=M$3),"X",""))</f>
-        <v>X</v>
+        <v>A</v>
       </c>
       <c r="N31" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I31&lt;&gt;"",WBS!$I31&lt;=N$3+6,WBS!$J31&gt;=N$3),"A",IF(AND(WBS!$F31&lt;=N$3+6,WBS!$G31&gt;=N$3),"X",""))</f>
@@ -5846,7 +6568,7 @@
       </c>
       <c r="C32" s="4" t="str">
         <f aca="false">WBS!E32</f>
-        <v>Menunggu</v>
+        <v>Selesai</v>
       </c>
       <c r="D32" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I32&lt;&gt;"",WBS!$I32&lt;=D$3+6,WBS!$J32&gt;=D$3),"A",IF(AND(WBS!$F32&lt;=D$3+6,WBS!$G32&gt;=D$3),"X",""))</f>
@@ -5886,7 +6608,7 @@
       </c>
       <c r="M32" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I32&lt;&gt;"",WBS!$I32&lt;=M$3+6,WBS!$J32&gt;=M$3),"A",IF(AND(WBS!$F32&lt;=M$3+6,WBS!$G32&gt;=M$3),"X",""))</f>
-        <v>X</v>
+        <v>A</v>
       </c>
       <c r="N32" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I32&lt;&gt;"",WBS!$I32&lt;=N$3+6,WBS!$J32&gt;=N$3),"A",IF(AND(WBS!$F32&lt;=N$3+6,WBS!$G32&gt;=N$3),"X",""))</f>
@@ -5916,7 +6638,7 @@
       </c>
       <c r="C33" s="4" t="str">
         <f aca="false">WBS!E33</f>
-        <v>Menunggu</v>
+        <v>Selesai</v>
       </c>
       <c r="D33" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I33&lt;&gt;"",WBS!$I33&lt;=D$3+6,WBS!$J33&gt;=D$3),"A",IF(AND(WBS!$F33&lt;=D$3+6,WBS!$G33&gt;=D$3),"X",""))</f>
@@ -5956,7 +6678,7 @@
       </c>
       <c r="M33" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I33&lt;&gt;"",WBS!$I33&lt;=M$3+6,WBS!$J33&gt;=M$3),"A",IF(AND(WBS!$F33&lt;=M$3+6,WBS!$G33&gt;=M$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="N33" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I33&lt;&gt;"",WBS!$I33&lt;=N$3+6,WBS!$J33&gt;=N$3),"A",IF(AND(WBS!$F33&lt;=N$3+6,WBS!$G33&gt;=N$3),"X",""))</f>
@@ -5986,7 +6708,7 @@
       </c>
       <c r="C34" s="4" t="str">
         <f aca="false">WBS!E34</f>
-        <v>Menunggu</v>
+        <v>Selesai</v>
       </c>
       <c r="D34" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I34&lt;&gt;"",WBS!$I34&lt;=D$3+6,WBS!$J34&gt;=D$3),"A",IF(AND(WBS!$F34&lt;=D$3+6,WBS!$G34&gt;=D$3),"X",""))</f>
@@ -6026,7 +6748,7 @@
       </c>
       <c r="M34" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I34&lt;&gt;"",WBS!$I34&lt;=M$3+6,WBS!$J34&gt;=M$3),"A",IF(AND(WBS!$F34&lt;=M$3+6,WBS!$G34&gt;=M$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="N34" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I34&lt;&gt;"",WBS!$I34&lt;=N$3+6,WBS!$J34&gt;=N$3),"A",IF(AND(WBS!$F34&lt;=N$3+6,WBS!$G34&gt;=N$3),"X",""))</f>
@@ -6052,11 +6774,11 @@
       </c>
       <c r="B35" s="5" t="str">
         <f aca="false">WBS!C35</f>
-        <v>Issue #1 - skeleton repo</v>
+        <v>Issue #1 sebagai uji perdana loop</v>
       </c>
       <c r="C35" s="4" t="str">
         <f aca="false">WBS!E35</f>
-        <v>Menunggu</v>
+        <v>Selesai</v>
       </c>
       <c r="D35" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I35&lt;&gt;"",WBS!$I35&lt;=D$3+6,WBS!$J35&gt;=D$3),"A",IF(AND(WBS!$F35&lt;=D$3+6,WBS!$G35&gt;=D$3),"X",""))</f>
@@ -6096,7 +6818,7 @@
       </c>
       <c r="M35" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I35&lt;&gt;"",WBS!$I35&lt;=M$3+6,WBS!$J35&gt;=M$3),"A",IF(AND(WBS!$F35&lt;=M$3+6,WBS!$G35&gt;=M$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="N35" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I35&lt;&gt;"",WBS!$I35&lt;=N$3+6,WBS!$J35&gt;=N$3),"A",IF(AND(WBS!$F35&lt;=N$3+6,WBS!$G35&gt;=N$3),"X",""))</f>
@@ -6126,7 +6848,7 @@
       </c>
       <c r="C36" s="4" t="str">
         <f aca="false">WBS!E36</f>
-        <v>Terblokir</v>
+        <v>Selesai</v>
       </c>
       <c r="D36" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I36&lt;&gt;"",WBS!$I36&lt;=D$3+6,WBS!$J36&gt;=D$3),"A",IF(AND(WBS!$F36&lt;=D$3+6,WBS!$G36&gt;=D$3),"X",""))</f>
@@ -6166,7 +6888,7 @@
       </c>
       <c r="M36" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I36&lt;&gt;"",WBS!$I36&lt;=M$3+6,WBS!$J36&gt;=M$3),"A",IF(AND(WBS!$F36&lt;=M$3+6,WBS!$G36&gt;=M$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="N36" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I36&lt;&gt;"",WBS!$I36&lt;=N$3+6,WBS!$J36&gt;=N$3),"A",IF(AND(WBS!$F36&lt;=N$3+6,WBS!$G36&gt;=N$3),"X",""))</f>
@@ -6196,7 +6918,7 @@
       </c>
       <c r="C37" s="4" t="str">
         <f aca="false">WBS!E37</f>
-        <v>Terblokir</v>
+        <v>Selesai</v>
       </c>
       <c r="D37" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I37&lt;&gt;"",WBS!$I37&lt;=D$3+6,WBS!$J37&gt;=D$3),"A",IF(AND(WBS!$F37&lt;=D$3+6,WBS!$G37&gt;=D$3),"X",""))</f>
@@ -6236,7 +6958,7 @@
       </c>
       <c r="M37" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I37&lt;&gt;"",WBS!$I37&lt;=M$3+6,WBS!$J37&gt;=M$3),"A",IF(AND(WBS!$F37&lt;=M$3+6,WBS!$G37&gt;=M$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="N37" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I37&lt;&gt;"",WBS!$I37&lt;=N$3+6,WBS!$J37&gt;=N$3),"A",IF(AND(WBS!$F37&lt;=N$3+6,WBS!$G37&gt;=N$3),"X",""))</f>
@@ -6266,7 +6988,7 @@
       </c>
       <c r="C38" s="4" t="str">
         <f aca="false">WBS!E38</f>
-        <v>Terblokir</v>
+        <v>Selesai</v>
       </c>
       <c r="D38" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I38&lt;&gt;"",WBS!$I38&lt;=D$3+6,WBS!$J38&gt;=D$3),"A",IF(AND(WBS!$F38&lt;=D$3+6,WBS!$G38&gt;=D$3),"X",""))</f>
@@ -6306,7 +7028,7 @@
       </c>
       <c r="M38" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I38&lt;&gt;"",WBS!$I38&lt;=M$3+6,WBS!$J38&gt;=M$3),"A",IF(AND(WBS!$F38&lt;=M$3+6,WBS!$G38&gt;=M$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="N38" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I38&lt;&gt;"",WBS!$I38&lt;=N$3+6,WBS!$J38&gt;=N$3),"A",IF(AND(WBS!$F38&lt;=N$3+6,WBS!$G38&gt;=N$3),"X",""))</f>
@@ -6336,7 +7058,7 @@
       </c>
       <c r="C39" s="4" t="str">
         <f aca="false">WBS!E39</f>
-        <v>Terblokir</v>
+        <v>Selesai</v>
       </c>
       <c r="D39" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I39&lt;&gt;"",WBS!$I39&lt;=D$3+6,WBS!$J39&gt;=D$3),"A",IF(AND(WBS!$F39&lt;=D$3+6,WBS!$G39&gt;=D$3),"X",""))</f>
@@ -6376,7 +7098,7 @@
       </c>
       <c r="M39" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I39&lt;&gt;"",WBS!$I39&lt;=M$3+6,WBS!$J39&gt;=M$3),"A",IF(AND(WBS!$F39&lt;=M$3+6,WBS!$G39&gt;=M$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="N39" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I39&lt;&gt;"",WBS!$I39&lt;=N$3+6,WBS!$J39&gt;=N$3),"A",IF(AND(WBS!$F39&lt;=N$3+6,WBS!$G39&gt;=N$3),"X",""))</f>
@@ -6406,7 +7128,7 @@
       </c>
       <c r="C40" s="4" t="str">
         <f aca="false">WBS!E40</f>
-        <v>Terblokir</v>
+        <v>Selesai</v>
       </c>
       <c r="D40" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I40&lt;&gt;"",WBS!$I40&lt;=D$3+6,WBS!$J40&gt;=D$3),"A",IF(AND(WBS!$F40&lt;=D$3+6,WBS!$G40&gt;=D$3),"X",""))</f>
@@ -6446,7 +7168,7 @@
       </c>
       <c r="M40" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I40&lt;&gt;"",WBS!$I40&lt;=M$3+6,WBS!$J40&gt;=M$3),"A",IF(AND(WBS!$F40&lt;=M$3+6,WBS!$G40&gt;=M$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="N40" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I40&lt;&gt;"",WBS!$I40&lt;=N$3+6,WBS!$J40&gt;=N$3),"A",IF(AND(WBS!$F40&lt;=N$3+6,WBS!$G40&gt;=N$3),"X",""))</f>
@@ -6476,7 +7198,7 @@
       </c>
       <c r="C41" s="4" t="str">
         <f aca="false">WBS!E41</f>
-        <v>Terblokir</v>
+        <v>Belum teruji</v>
       </c>
       <c r="D41" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I41&lt;&gt;"",WBS!$I41&lt;=D$3+6,WBS!$J41&gt;=D$3),"A",IF(AND(WBS!$F41&lt;=D$3+6,WBS!$G41&gt;=D$3),"X",""))</f>
@@ -6546,7 +7268,7 @@
       </c>
       <c r="C42" s="4" t="str">
         <f aca="false">WBS!E42</f>
-        <v>Terblokir</v>
+        <v>Selesai</v>
       </c>
       <c r="D42" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I42&lt;&gt;"",WBS!$I42&lt;=D$3+6,WBS!$J42&gt;=D$3),"A",IF(AND(WBS!$F42&lt;=D$3+6,WBS!$G42&gt;=D$3),"X",""))</f>
@@ -6586,7 +7308,7 @@
       </c>
       <c r="M42" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I42&lt;&gt;"",WBS!$I42&lt;=M$3+6,WBS!$J42&gt;=M$3),"A",IF(AND(WBS!$F42&lt;=M$3+6,WBS!$G42&gt;=M$3),"X",""))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="N42" s="4" t="str">
         <f aca="false">IF(AND(WBS!$I42&lt;&gt;"",WBS!$I42&lt;=N$3+6,WBS!$J42&gt;=N$3),"A",IF(AND(WBS!$F42&lt;=N$3+6,WBS!$G42&gt;=N$3),"X",""))</f>
@@ -6885,20 +7607,720 @@
         <v/>
       </c>
     </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="str">
+        <f aca="false">WBS!A47</f>
+        <v>9.1</v>
+      </c>
+      <c r="B47" s="5" t="str">
+        <f aca="false">WBS!C47</f>
+        <v>Pisahkan tahap rencana ke agent-plan.yml</v>
+      </c>
+      <c r="C47" s="4" t="str">
+        <f aca="false">WBS!E47</f>
+        <v>Selesai</v>
+      </c>
+      <c r="D47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=D$3+6,WBS!$J47&gt;=D$3),"A",IF(AND(WBS!$F47&lt;=D$3+6,WBS!$G47&gt;=D$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="E47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=E$3+6,WBS!$J47&gt;=E$3),"A",IF(AND(WBS!$F47&lt;=E$3+6,WBS!$G47&gt;=E$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="F47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=F$3+6,WBS!$J47&gt;=F$3),"A",IF(AND(WBS!$F47&lt;=F$3+6,WBS!$G47&gt;=F$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="G47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=G$3+6,WBS!$J47&gt;=G$3),"A",IF(AND(WBS!$F47&lt;=G$3+6,WBS!$G47&gt;=G$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="H47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=H$3+6,WBS!$J47&gt;=H$3),"A",IF(AND(WBS!$F47&lt;=H$3+6,WBS!$G47&gt;=H$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="I47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=I$3+6,WBS!$J47&gt;=I$3),"A",IF(AND(WBS!$F47&lt;=I$3+6,WBS!$G47&gt;=I$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="J47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=J$3+6,WBS!$J47&gt;=J$3),"A",IF(AND(WBS!$F47&lt;=J$3+6,WBS!$G47&gt;=J$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="K47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=K$3+6,WBS!$J47&gt;=K$3),"A",IF(AND(WBS!$F47&lt;=K$3+6,WBS!$G47&gt;=K$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="L47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=L$3+6,WBS!$J47&gt;=L$3),"A",IF(AND(WBS!$F47&lt;=L$3+6,WBS!$G47&gt;=L$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="M47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=M$3+6,WBS!$J47&gt;=M$3),"A",IF(AND(WBS!$F47&lt;=M$3+6,WBS!$G47&gt;=M$3),"X",""))</f>
+        <v>A</v>
+      </c>
+      <c r="N47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=N$3+6,WBS!$J47&gt;=N$3),"A",IF(AND(WBS!$F47&lt;=N$3+6,WBS!$G47&gt;=N$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="O47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=O$3+6,WBS!$J47&gt;=O$3),"A",IF(AND(WBS!$F47&lt;=O$3+6,WBS!$G47&gt;=O$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="P47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=P$3+6,WBS!$J47&gt;=P$3),"A",IF(AND(WBS!$F47&lt;=P$3+6,WBS!$G47&gt;=P$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="Q47" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I47&lt;&gt;"",WBS!$I47&lt;=Q$3+6,WBS!$J47&gt;=Q$3),"A",IF(AND(WBS!$F47&lt;=Q$3+6,WBS!$G47&gt;=Q$3),"X",""))</f>
+        <v/>
+      </c>
+    </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="32" t="s">
-        <v>180</v>
+      <c r="A48" s="4" t="str">
+        <f aca="false">WBS!A48</f>
+        <v>9.2</v>
+      </c>
+      <c r="B48" s="5" t="str">
+        <f aca="false">WBS!C48</f>
+        <v>Konfigurasi model lewat repository variables</v>
+      </c>
+      <c r="C48" s="4" t="str">
+        <f aca="false">WBS!E48</f>
+        <v>Selesai</v>
+      </c>
+      <c r="D48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=D$3+6,WBS!$J48&gt;=D$3),"A",IF(AND(WBS!$F48&lt;=D$3+6,WBS!$G48&gt;=D$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="E48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=E$3+6,WBS!$J48&gt;=E$3),"A",IF(AND(WBS!$F48&lt;=E$3+6,WBS!$G48&gt;=E$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="F48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=F$3+6,WBS!$J48&gt;=F$3),"A",IF(AND(WBS!$F48&lt;=F$3+6,WBS!$G48&gt;=F$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="G48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=G$3+6,WBS!$J48&gt;=G$3),"A",IF(AND(WBS!$F48&lt;=G$3+6,WBS!$G48&gt;=G$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="H48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=H$3+6,WBS!$J48&gt;=H$3),"A",IF(AND(WBS!$F48&lt;=H$3+6,WBS!$G48&gt;=H$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="I48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=I$3+6,WBS!$J48&gt;=I$3),"A",IF(AND(WBS!$F48&lt;=I$3+6,WBS!$G48&gt;=I$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="J48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=J$3+6,WBS!$J48&gt;=J$3),"A",IF(AND(WBS!$F48&lt;=J$3+6,WBS!$G48&gt;=J$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="K48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=K$3+6,WBS!$J48&gt;=K$3),"A",IF(AND(WBS!$F48&lt;=K$3+6,WBS!$G48&gt;=K$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="L48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=L$3+6,WBS!$J48&gt;=L$3),"A",IF(AND(WBS!$F48&lt;=L$3+6,WBS!$G48&gt;=L$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="M48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=M$3+6,WBS!$J48&gt;=M$3),"A",IF(AND(WBS!$F48&lt;=M$3+6,WBS!$G48&gt;=M$3),"X",""))</f>
+        <v>A</v>
+      </c>
+      <c r="N48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=N$3+6,WBS!$J48&gt;=N$3),"A",IF(AND(WBS!$F48&lt;=N$3+6,WBS!$G48&gt;=N$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="O48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=O$3+6,WBS!$J48&gt;=O$3),"A",IF(AND(WBS!$F48&lt;=O$3+6,WBS!$G48&gt;=O$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="P48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=P$3+6,WBS!$J48&gt;=P$3),"A",IF(AND(WBS!$F48&lt;=P$3+6,WBS!$G48&gt;=P$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="Q48" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I48&lt;&gt;"",WBS!$I48&lt;=Q$3+6,WBS!$J48&gt;=Q$3),"A",IF(AND(WBS!$F48&lt;=Q$3+6,WBS!$G48&gt;=Q$3),"X",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="str">
+        <f aca="false">WBS!A49</f>
+        <v>9.3</v>
+      </c>
+      <c r="B49" s="5" t="str">
+        <f aca="false">WBS!C49</f>
+        <v>Streaming log, batas waktu percobaan, preflight gateway</v>
+      </c>
+      <c r="C49" s="4" t="str">
+        <f aca="false">WBS!E49</f>
+        <v>Selesai</v>
+      </c>
+      <c r="D49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=D$3+6,WBS!$J49&gt;=D$3),"A",IF(AND(WBS!$F49&lt;=D$3+6,WBS!$G49&gt;=D$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="E49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=E$3+6,WBS!$J49&gt;=E$3),"A",IF(AND(WBS!$F49&lt;=E$3+6,WBS!$G49&gt;=E$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="F49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=F$3+6,WBS!$J49&gt;=F$3),"A",IF(AND(WBS!$F49&lt;=F$3+6,WBS!$G49&gt;=F$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="G49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=G$3+6,WBS!$J49&gt;=G$3),"A",IF(AND(WBS!$F49&lt;=G$3+6,WBS!$G49&gt;=G$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="H49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=H$3+6,WBS!$J49&gt;=H$3),"A",IF(AND(WBS!$F49&lt;=H$3+6,WBS!$G49&gt;=H$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="I49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=I$3+6,WBS!$J49&gt;=I$3),"A",IF(AND(WBS!$F49&lt;=I$3+6,WBS!$G49&gt;=I$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="J49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=J$3+6,WBS!$J49&gt;=J$3),"A",IF(AND(WBS!$F49&lt;=J$3+6,WBS!$G49&gt;=J$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="K49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=K$3+6,WBS!$J49&gt;=K$3),"A",IF(AND(WBS!$F49&lt;=K$3+6,WBS!$G49&gt;=K$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="L49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=L$3+6,WBS!$J49&gt;=L$3),"A",IF(AND(WBS!$F49&lt;=L$3+6,WBS!$G49&gt;=L$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="M49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=M$3+6,WBS!$J49&gt;=M$3),"A",IF(AND(WBS!$F49&lt;=M$3+6,WBS!$G49&gt;=M$3),"X",""))</f>
+        <v>A</v>
+      </c>
+      <c r="N49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=N$3+6,WBS!$J49&gt;=N$3),"A",IF(AND(WBS!$F49&lt;=N$3+6,WBS!$G49&gt;=N$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="O49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=O$3+6,WBS!$J49&gt;=O$3),"A",IF(AND(WBS!$F49&lt;=O$3+6,WBS!$G49&gt;=O$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="P49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=P$3+6,WBS!$J49&gt;=P$3),"A",IF(AND(WBS!$F49&lt;=P$3+6,WBS!$G49&gt;=P$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="Q49" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I49&lt;&gt;"",WBS!$I49&lt;=Q$3+6,WBS!$J49&gt;=Q$3),"A",IF(AND(WBS!$F49&lt;=Q$3+6,WBS!$G49&gt;=Q$3),"X",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="str">
+        <f aca="false">WBS!A50</f>
+        <v>9.4</v>
+      </c>
+      <c r="B50" s="5" t="str">
+        <f aca="false">WBS!C50</f>
+        <v>Selaraskan preflight dengan konfigurasi tanpa fallback</v>
+      </c>
+      <c r="C50" s="4" t="str">
+        <f aca="false">WBS!E50</f>
+        <v>Selesai</v>
+      </c>
+      <c r="D50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=D$3+6,WBS!$J50&gt;=D$3),"A",IF(AND(WBS!$F50&lt;=D$3+6,WBS!$G50&gt;=D$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="E50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=E$3+6,WBS!$J50&gt;=E$3),"A",IF(AND(WBS!$F50&lt;=E$3+6,WBS!$G50&gt;=E$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="F50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=F$3+6,WBS!$J50&gt;=F$3),"A",IF(AND(WBS!$F50&lt;=F$3+6,WBS!$G50&gt;=F$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="G50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=G$3+6,WBS!$J50&gt;=G$3),"A",IF(AND(WBS!$F50&lt;=G$3+6,WBS!$G50&gt;=G$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="H50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=H$3+6,WBS!$J50&gt;=H$3),"A",IF(AND(WBS!$F50&lt;=H$3+6,WBS!$G50&gt;=H$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="I50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=I$3+6,WBS!$J50&gt;=I$3),"A",IF(AND(WBS!$F50&lt;=I$3+6,WBS!$G50&gt;=I$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="J50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=J$3+6,WBS!$J50&gt;=J$3),"A",IF(AND(WBS!$F50&lt;=J$3+6,WBS!$G50&gt;=J$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="K50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=K$3+6,WBS!$J50&gt;=K$3),"A",IF(AND(WBS!$F50&lt;=K$3+6,WBS!$G50&gt;=K$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="L50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=L$3+6,WBS!$J50&gt;=L$3),"A",IF(AND(WBS!$F50&lt;=L$3+6,WBS!$G50&gt;=L$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="M50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=M$3+6,WBS!$J50&gt;=M$3),"A",IF(AND(WBS!$F50&lt;=M$3+6,WBS!$G50&gt;=M$3),"X",""))</f>
+        <v>A</v>
+      </c>
+      <c r="N50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=N$3+6,WBS!$J50&gt;=N$3),"A",IF(AND(WBS!$F50&lt;=N$3+6,WBS!$G50&gt;=N$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="O50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=O$3+6,WBS!$J50&gt;=O$3),"A",IF(AND(WBS!$F50&lt;=O$3+6,WBS!$G50&gt;=O$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="P50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=P$3+6,WBS!$J50&gt;=P$3),"A",IF(AND(WBS!$F50&lt;=P$3+6,WBS!$G50&gt;=P$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="Q50" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I50&lt;&gt;"",WBS!$I50&lt;=Q$3+6,WBS!$J50&gt;=Q$3),"A",IF(AND(WBS!$F50&lt;=Q$3+6,WBS!$G50&gt;=Q$3),"X",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="str">
+        <f aca="false">WBS!A51</f>
+        <v>9.5</v>
+      </c>
+      <c r="B51" s="5" t="str">
+        <f aca="false">WBS!C51</f>
+        <v>Seragamkan token agent-fix ke CODE_API_KEY</v>
+      </c>
+      <c r="C51" s="4" t="str">
+        <f aca="false">WBS!E51</f>
+        <v>Selesai</v>
+      </c>
+      <c r="D51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=D$3+6,WBS!$J51&gt;=D$3),"A",IF(AND(WBS!$F51&lt;=D$3+6,WBS!$G51&gt;=D$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="E51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=E$3+6,WBS!$J51&gt;=E$3),"A",IF(AND(WBS!$F51&lt;=E$3+6,WBS!$G51&gt;=E$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="F51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=F$3+6,WBS!$J51&gt;=F$3),"A",IF(AND(WBS!$F51&lt;=F$3+6,WBS!$G51&gt;=F$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="G51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=G$3+6,WBS!$J51&gt;=G$3),"A",IF(AND(WBS!$F51&lt;=G$3+6,WBS!$G51&gt;=G$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="H51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=H$3+6,WBS!$J51&gt;=H$3),"A",IF(AND(WBS!$F51&lt;=H$3+6,WBS!$G51&gt;=H$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="I51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=I$3+6,WBS!$J51&gt;=I$3),"A",IF(AND(WBS!$F51&lt;=I$3+6,WBS!$G51&gt;=I$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="J51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=J$3+6,WBS!$J51&gt;=J$3),"A",IF(AND(WBS!$F51&lt;=J$3+6,WBS!$G51&gt;=J$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="K51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=K$3+6,WBS!$J51&gt;=K$3),"A",IF(AND(WBS!$F51&lt;=K$3+6,WBS!$G51&gt;=K$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="L51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=L$3+6,WBS!$J51&gt;=L$3),"A",IF(AND(WBS!$F51&lt;=L$3+6,WBS!$G51&gt;=L$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="M51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=M$3+6,WBS!$J51&gt;=M$3),"A",IF(AND(WBS!$F51&lt;=M$3+6,WBS!$G51&gt;=M$3),"X",""))</f>
+        <v>A</v>
+      </c>
+      <c r="N51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=N$3+6,WBS!$J51&gt;=N$3),"A",IF(AND(WBS!$F51&lt;=N$3+6,WBS!$G51&gt;=N$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="O51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=O$3+6,WBS!$J51&gt;=O$3),"A",IF(AND(WBS!$F51&lt;=O$3+6,WBS!$G51&gt;=O$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="P51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=P$3+6,WBS!$J51&gt;=P$3),"A",IF(AND(WBS!$F51&lt;=P$3+6,WBS!$G51&gt;=P$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="Q51" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I51&lt;&gt;"",WBS!$I51&lt;=Q$3+6,WBS!$J51&gt;=Q$3),"A",IF(AND(WBS!$F51&lt;=Q$3+6,WBS!$G51&gt;=Q$3),"X",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="str">
+        <f aca="false">WBS!A52</f>
+        <v>9.6</v>
+      </c>
+      <c r="B52" s="5" t="str">
+        <f aca="false">WBS!C52</f>
+        <v>Perbaikan gateway Cloudflare 524</v>
+      </c>
+      <c r="C52" s="4" t="str">
+        <f aca="false">WBS!E52</f>
+        <v>Selesai</v>
+      </c>
+      <c r="D52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=D$3+6,WBS!$J52&gt;=D$3),"A",IF(AND(WBS!$F52&lt;=D$3+6,WBS!$G52&gt;=D$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="E52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=E$3+6,WBS!$J52&gt;=E$3),"A",IF(AND(WBS!$F52&lt;=E$3+6,WBS!$G52&gt;=E$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="F52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=F$3+6,WBS!$J52&gt;=F$3),"A",IF(AND(WBS!$F52&lt;=F$3+6,WBS!$G52&gt;=F$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="G52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=G$3+6,WBS!$J52&gt;=G$3),"A",IF(AND(WBS!$F52&lt;=G$3+6,WBS!$G52&gt;=G$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="H52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=H$3+6,WBS!$J52&gt;=H$3),"A",IF(AND(WBS!$F52&lt;=H$3+6,WBS!$G52&gt;=H$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="I52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=I$3+6,WBS!$J52&gt;=I$3),"A",IF(AND(WBS!$F52&lt;=I$3+6,WBS!$G52&gt;=I$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="J52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=J$3+6,WBS!$J52&gt;=J$3),"A",IF(AND(WBS!$F52&lt;=J$3+6,WBS!$G52&gt;=J$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="K52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=K$3+6,WBS!$J52&gt;=K$3),"A",IF(AND(WBS!$F52&lt;=K$3+6,WBS!$G52&gt;=K$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="L52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=L$3+6,WBS!$J52&gt;=L$3),"A",IF(AND(WBS!$F52&lt;=L$3+6,WBS!$G52&gt;=L$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="M52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=M$3+6,WBS!$J52&gt;=M$3),"A",IF(AND(WBS!$F52&lt;=M$3+6,WBS!$G52&gt;=M$3),"X",""))</f>
+        <v>A</v>
+      </c>
+      <c r="N52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=N$3+6,WBS!$J52&gt;=N$3),"A",IF(AND(WBS!$F52&lt;=N$3+6,WBS!$G52&gt;=N$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="O52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=O$3+6,WBS!$J52&gt;=O$3),"A",IF(AND(WBS!$F52&lt;=O$3+6,WBS!$G52&gt;=O$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="P52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=P$3+6,WBS!$J52&gt;=P$3),"A",IF(AND(WBS!$F52&lt;=P$3+6,WBS!$G52&gt;=P$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="Q52" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I52&lt;&gt;"",WBS!$I52&lt;=Q$3+6,WBS!$J52&gt;=Q$3),"A",IF(AND(WBS!$F52&lt;=Q$3+6,WBS!$G52&gt;=Q$3),"X",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="str">
+        <f aca="false">WBS!A53</f>
+        <v>9.7</v>
+      </c>
+      <c r="B53" s="5" t="str">
+        <f aca="false">WBS!C53</f>
+        <v>Laporkan penyebab kegagalan sebenarnya</v>
+      </c>
+      <c r="C53" s="4" t="str">
+        <f aca="false">WBS!E53</f>
+        <v>Selesai</v>
+      </c>
+      <c r="D53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=D$3+6,WBS!$J53&gt;=D$3),"A",IF(AND(WBS!$F53&lt;=D$3+6,WBS!$G53&gt;=D$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="E53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=E$3+6,WBS!$J53&gt;=E$3),"A",IF(AND(WBS!$F53&lt;=E$3+6,WBS!$G53&gt;=E$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="F53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=F$3+6,WBS!$J53&gt;=F$3),"A",IF(AND(WBS!$F53&lt;=F$3+6,WBS!$G53&gt;=F$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="G53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=G$3+6,WBS!$J53&gt;=G$3),"A",IF(AND(WBS!$F53&lt;=G$3+6,WBS!$G53&gt;=G$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="H53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=H$3+6,WBS!$J53&gt;=H$3),"A",IF(AND(WBS!$F53&lt;=H$3+6,WBS!$G53&gt;=H$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="I53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=I$3+6,WBS!$J53&gt;=I$3),"A",IF(AND(WBS!$F53&lt;=I$3+6,WBS!$G53&gt;=I$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="J53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=J$3+6,WBS!$J53&gt;=J$3),"A",IF(AND(WBS!$F53&lt;=J$3+6,WBS!$G53&gt;=J$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="K53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=K$3+6,WBS!$J53&gt;=K$3),"A",IF(AND(WBS!$F53&lt;=K$3+6,WBS!$G53&gt;=K$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="L53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=L$3+6,WBS!$J53&gt;=L$3),"A",IF(AND(WBS!$F53&lt;=L$3+6,WBS!$G53&gt;=L$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="M53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=M$3+6,WBS!$J53&gt;=M$3),"A",IF(AND(WBS!$F53&lt;=M$3+6,WBS!$G53&gt;=M$3),"X",""))</f>
+        <v>A</v>
+      </c>
+      <c r="N53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=N$3+6,WBS!$J53&gt;=N$3),"A",IF(AND(WBS!$F53&lt;=N$3+6,WBS!$G53&gt;=N$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="O53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=O$3+6,WBS!$J53&gt;=O$3),"A",IF(AND(WBS!$F53&lt;=O$3+6,WBS!$G53&gt;=O$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="P53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=P$3+6,WBS!$J53&gt;=P$3),"A",IF(AND(WBS!$F53&lt;=P$3+6,WBS!$G53&gt;=P$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="Q53" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I53&lt;&gt;"",WBS!$I53&lt;=Q$3+6,WBS!$J53&gt;=Q$3),"A",IF(AND(WBS!$F53&lt;=Q$3+6,WBS!$G53&gt;=Q$3),"X",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="str">
+        <f aca="false">WBS!A54</f>
+        <v>9.8</v>
+      </c>
+      <c r="B54" s="5" t="str">
+        <f aca="false">WBS!C54</f>
+        <v>Empat cacat dari siklus penuh pertama</v>
+      </c>
+      <c r="C54" s="4" t="str">
+        <f aca="false">WBS!E54</f>
+        <v>Selesai</v>
+      </c>
+      <c r="D54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=D$3+6,WBS!$J54&gt;=D$3),"A",IF(AND(WBS!$F54&lt;=D$3+6,WBS!$G54&gt;=D$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="E54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=E$3+6,WBS!$J54&gt;=E$3),"A",IF(AND(WBS!$F54&lt;=E$3+6,WBS!$G54&gt;=E$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="F54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=F$3+6,WBS!$J54&gt;=F$3),"A",IF(AND(WBS!$F54&lt;=F$3+6,WBS!$G54&gt;=F$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="G54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=G$3+6,WBS!$J54&gt;=G$3),"A",IF(AND(WBS!$F54&lt;=G$3+6,WBS!$G54&gt;=G$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="H54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=H$3+6,WBS!$J54&gt;=H$3),"A",IF(AND(WBS!$F54&lt;=H$3+6,WBS!$G54&gt;=H$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="I54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=I$3+6,WBS!$J54&gt;=I$3),"A",IF(AND(WBS!$F54&lt;=I$3+6,WBS!$G54&gt;=I$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="J54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=J$3+6,WBS!$J54&gt;=J$3),"A",IF(AND(WBS!$F54&lt;=J$3+6,WBS!$G54&gt;=J$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="K54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=K$3+6,WBS!$J54&gt;=K$3),"A",IF(AND(WBS!$F54&lt;=K$3+6,WBS!$G54&gt;=K$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="L54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=L$3+6,WBS!$J54&gt;=L$3),"A",IF(AND(WBS!$F54&lt;=L$3+6,WBS!$G54&gt;=L$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="M54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=M$3+6,WBS!$J54&gt;=M$3),"A",IF(AND(WBS!$F54&lt;=M$3+6,WBS!$G54&gt;=M$3),"X",""))</f>
+        <v>A</v>
+      </c>
+      <c r="N54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=N$3+6,WBS!$J54&gt;=N$3),"A",IF(AND(WBS!$F54&lt;=N$3+6,WBS!$G54&gt;=N$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="O54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=O$3+6,WBS!$J54&gt;=O$3),"A",IF(AND(WBS!$F54&lt;=O$3+6,WBS!$G54&gt;=O$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="P54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=P$3+6,WBS!$J54&gt;=P$3),"A",IF(AND(WBS!$F54&lt;=P$3+6,WBS!$G54&gt;=P$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="Q54" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I54&lt;&gt;"",WBS!$I54&lt;=Q$3+6,WBS!$J54&gt;=Q$3),"A",IF(AND(WBS!$F54&lt;=Q$3+6,WBS!$G54&gt;=Q$3),"X",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="str">
+        <f aca="false">WBS!A55</f>
+        <v>9.9</v>
+      </c>
+      <c r="B55" s="5" t="str">
+        <f aca="false">WBS!C55</f>
+        <v>Pulihkan circuit breaker dan footer commit</v>
+      </c>
+      <c r="C55" s="4" t="str">
+        <f aca="false">WBS!E55</f>
+        <v>Selesai</v>
+      </c>
+      <c r="D55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=D$3+6,WBS!$J55&gt;=D$3),"A",IF(AND(WBS!$F55&lt;=D$3+6,WBS!$G55&gt;=D$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="E55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=E$3+6,WBS!$J55&gt;=E$3),"A",IF(AND(WBS!$F55&lt;=E$3+6,WBS!$G55&gt;=E$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="F55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=F$3+6,WBS!$J55&gt;=F$3),"A",IF(AND(WBS!$F55&lt;=F$3+6,WBS!$G55&gt;=F$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="G55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=G$3+6,WBS!$J55&gt;=G$3),"A",IF(AND(WBS!$F55&lt;=G$3+6,WBS!$G55&gt;=G$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="H55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=H$3+6,WBS!$J55&gt;=H$3),"A",IF(AND(WBS!$F55&lt;=H$3+6,WBS!$G55&gt;=H$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="I55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=I$3+6,WBS!$J55&gt;=I$3),"A",IF(AND(WBS!$F55&lt;=I$3+6,WBS!$G55&gt;=I$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="J55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=J$3+6,WBS!$J55&gt;=J$3),"A",IF(AND(WBS!$F55&lt;=J$3+6,WBS!$G55&gt;=J$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="K55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=K$3+6,WBS!$J55&gt;=K$3),"A",IF(AND(WBS!$F55&lt;=K$3+6,WBS!$G55&gt;=K$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="L55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=L$3+6,WBS!$J55&gt;=L$3),"A",IF(AND(WBS!$F55&lt;=L$3+6,WBS!$G55&gt;=L$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="M55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=M$3+6,WBS!$J55&gt;=M$3),"A",IF(AND(WBS!$F55&lt;=M$3+6,WBS!$G55&gt;=M$3),"X",""))</f>
+        <v>A</v>
+      </c>
+      <c r="N55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=N$3+6,WBS!$J55&gt;=N$3),"A",IF(AND(WBS!$F55&lt;=N$3+6,WBS!$G55&gt;=N$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="O55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=O$3+6,WBS!$J55&gt;=O$3),"A",IF(AND(WBS!$F55&lt;=O$3+6,WBS!$G55&gt;=O$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="P55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=P$3+6,WBS!$J55&gt;=P$3),"A",IF(AND(WBS!$F55&lt;=P$3+6,WBS!$G55&gt;=P$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="Q55" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I55&lt;&gt;"",WBS!$I55&lt;=Q$3+6,WBS!$J55&gt;=Q$3),"A",IF(AND(WBS!$F55&lt;=Q$3+6,WBS!$G55&gt;=Q$3),"X",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="str">
+        <f aca="false">WBS!A56</f>
+        <v>9.10</v>
+      </c>
+      <c r="B56" s="5" t="str">
+        <f aca="false">WBS!C56</f>
+        <v>Uji agent-plan.yml hasil pemisahan</v>
+      </c>
+      <c r="C56" s="4" t="str">
+        <f aca="false">WBS!E56</f>
+        <v>Belum teruji</v>
+      </c>
+      <c r="D56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=D$3+6,WBS!$J56&gt;=D$3),"A",IF(AND(WBS!$F56&lt;=D$3+6,WBS!$G56&gt;=D$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="E56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=E$3+6,WBS!$J56&gt;=E$3),"A",IF(AND(WBS!$F56&lt;=E$3+6,WBS!$G56&gt;=E$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="F56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=F$3+6,WBS!$J56&gt;=F$3),"A",IF(AND(WBS!$F56&lt;=F$3+6,WBS!$G56&gt;=F$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="G56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=G$3+6,WBS!$J56&gt;=G$3),"A",IF(AND(WBS!$F56&lt;=G$3+6,WBS!$G56&gt;=G$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="H56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=H$3+6,WBS!$J56&gt;=H$3),"A",IF(AND(WBS!$F56&lt;=H$3+6,WBS!$G56&gt;=H$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="I56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=I$3+6,WBS!$J56&gt;=I$3),"A",IF(AND(WBS!$F56&lt;=I$3+6,WBS!$G56&gt;=I$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="J56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=J$3+6,WBS!$J56&gt;=J$3),"A",IF(AND(WBS!$F56&lt;=J$3+6,WBS!$G56&gt;=J$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="K56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=K$3+6,WBS!$J56&gt;=K$3),"A",IF(AND(WBS!$F56&lt;=K$3+6,WBS!$G56&gt;=K$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="L56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=L$3+6,WBS!$J56&gt;=L$3),"A",IF(AND(WBS!$F56&lt;=L$3+6,WBS!$G56&gt;=L$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="M56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=M$3+6,WBS!$J56&gt;=M$3),"A",IF(AND(WBS!$F56&lt;=M$3+6,WBS!$G56&gt;=M$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="N56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=N$3+6,WBS!$J56&gt;=N$3),"A",IF(AND(WBS!$F56&lt;=N$3+6,WBS!$G56&gt;=N$3),"X",""))</f>
+        <v>X</v>
+      </c>
+      <c r="O56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=O$3+6,WBS!$J56&gt;=O$3),"A",IF(AND(WBS!$F56&lt;=O$3+6,WBS!$G56&gt;=O$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="P56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=P$3+6,WBS!$J56&gt;=P$3),"A",IF(AND(WBS!$F56&lt;=P$3+6,WBS!$G56&gt;=P$3),"X",""))</f>
+        <v/>
+      </c>
+      <c r="Q56" s="4" t="str">
+        <f aca="false">IF(AND(WBS!$I56&lt;&gt;"",WBS!$I56&lt;=Q$3+6,WBS!$J56&gt;=Q$3),"A",IF(AND(WBS!$F56&lt;=Q$3+6,WBS!$G56&gt;=Q$3),"X",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="34" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D5:Q46">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+  <conditionalFormatting sqref="D5:Q56">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>D5="A"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>AND(D5="X",$C5="Selesai")</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>AND(D5="X",$C5&lt;&gt;"Selesai")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6917,7 +8339,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
@@ -6935,20 +8357,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>22</v>
@@ -6972,555 +8394,601 @@
         <v>14</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A5)</f>
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A5)</f>
         <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A5,WBS!$E$5:$E$46,"Selesai")</f>
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A5,WBS!$E$5:$E$56,"Selesai")</f>
         <v>4</v>
       </c>
-      <c r="D5" s="34" t="n">
-        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$46,WBS!$B$5:$B$46,$A5)</f>
+      <c r="D5" s="36" t="n">
+        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$56,WBS!$B$5:$B$56,$A5)</f>
         <v>46204</v>
       </c>
-      <c r="E5" s="34" t="n">
-        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$46,WBS!$B$5:$B$46,$A5)</f>
+      <c r="E5" s="36" t="n">
+        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$56,WBS!$B$5:$B$56,$A5)</f>
         <v>46224</v>
       </c>
-      <c r="F5" s="34" t="n">
-        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A5)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A5))</f>
+      <c r="F5" s="36" t="n">
+        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A5)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A5))</f>
         <v>46204</v>
       </c>
-      <c r="G5" s="34" t="n">
-        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A5)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A5))</f>
+      <c r="G5" s="36" t="n">
+        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A5)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A5))</f>
         <v>46224</v>
       </c>
-      <c r="H5" s="35" t="n">
-        <f aca="false">SUMIFS(WBS!$L$5:$L$46,WBS!$B$5:$B$46,$A5)</f>
-        <v>0.0952380952380953</v>
-      </c>
-      <c r="I5" s="36" t="n">
-        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$46,WBS!$B$5:$B$46,$A5)/$H5,0)</f>
+      <c r="H5" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$B$5:$B$56,$A5)</f>
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I5" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$B$5:$B$56,$A5)/$H5,0)</f>
         <v>1</v>
       </c>
-      <c r="J5" s="37" t="s">
-        <v>188</v>
+      <c r="J5" s="39" t="s">
+        <v>218</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="35" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A6)</f>
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A6)</f>
         <v>4</v>
       </c>
       <c r="C6" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A6,WBS!$E$5:$E$46,"Selesai")</f>
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A6,WBS!$E$5:$E$56,"Selesai")</f>
         <v>4</v>
       </c>
-      <c r="D6" s="34" t="n">
-        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$46,WBS!$B$5:$B$46,$A6)</f>
+      <c r="D6" s="36" t="n">
+        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$56,WBS!$B$5:$B$56,$A6)</f>
         <v>46209</v>
       </c>
-      <c r="E6" s="34" t="n">
-        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$46,WBS!$B$5:$B$46,$A6)</f>
+      <c r="E6" s="36" t="n">
+        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$56,WBS!$B$5:$B$56,$A6)</f>
         <v>46220</v>
       </c>
-      <c r="F6" s="34" t="n">
-        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A6)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A6))</f>
+      <c r="F6" s="36" t="n">
+        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A6)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A6))</f>
         <v>46252</v>
       </c>
-      <c r="G6" s="34" t="n">
-        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A6)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A6))</f>
+      <c r="G6" s="36" t="n">
+        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A6)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A6))</f>
         <v>46252</v>
       </c>
-      <c r="H6" s="35" t="n">
-        <f aca="false">SUMIFS(WBS!$L$5:$L$46,WBS!$B$5:$B$46,$A6)</f>
-        <v>0.0952380952380953</v>
-      </c>
-      <c r="I6" s="36" t="n">
-        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$46,WBS!$B$5:$B$46,$A6)/$H6,0)</f>
+      <c r="H6" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$B$5:$B$56,$A6)</f>
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I6" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$B$5:$B$56,$A6)/$H6,0)</f>
         <v>1</v>
       </c>
-      <c r="J6" s="38" t="n">
+      <c r="J6" s="40" t="n">
         <v>0.22</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="35" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A7)</f>
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A7)</f>
         <v>9</v>
       </c>
       <c r="C7" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A7,WBS!$E$5:$E$46,"Selesai")</f>
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A7,WBS!$E$5:$E$56,"Selesai")</f>
         <v>9</v>
       </c>
-      <c r="D7" s="34" t="n">
-        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$46,WBS!$B$5:$B$46,$A7)</f>
+      <c r="D7" s="36" t="n">
+        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$56,WBS!$B$5:$B$56,$A7)</f>
         <v>46223</v>
       </c>
-      <c r="E7" s="34" t="n">
-        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$46,WBS!$B$5:$B$46,$A7)</f>
+      <c r="E7" s="36" t="n">
+        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$56,WBS!$B$5:$B$56,$A7)</f>
         <v>46239</v>
       </c>
-      <c r="F7" s="34" t="n">
-        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A7)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A7))</f>
+      <c r="F7" s="36" t="n">
+        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A7)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A7))</f>
         <v>46252</v>
       </c>
-      <c r="G7" s="34" t="n">
-        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A7)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A7))</f>
+      <c r="G7" s="36" t="n">
+        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A7)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A7))</f>
         <v>46252</v>
       </c>
-      <c r="H7" s="35" t="n">
-        <f aca="false">SUMIFS(WBS!$L$5:$L$46,WBS!$B$5:$B$46,$A7)</f>
-        <v>0.214285714285714</v>
-      </c>
-      <c r="I7" s="36" t="n">
-        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$46,WBS!$B$5:$B$46,$A7)/$H7,0)</f>
+      <c r="H7" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$B$5:$B$56,$A7)</f>
+        <v>0.173076923076923</v>
+      </c>
+      <c r="I7" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$B$5:$B$56,$A7)/$H7,0)</f>
         <v>1</v>
       </c>
-      <c r="J7" s="38" t="n">
+      <c r="J7" s="40" t="n">
         <v>0.09</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="35" t="s">
         <v>77</v>
       </c>
       <c r="B8" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A8)</f>
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A8)</f>
         <v>4</v>
       </c>
       <c r="C8" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A8,WBS!$E$5:$E$46,"Selesai")</f>
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A8,WBS!$E$5:$E$56,"Selesai")</f>
         <v>4</v>
       </c>
-      <c r="D8" s="34" t="n">
-        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$46,WBS!$B$5:$B$46,$A8)</f>
+      <c r="D8" s="36" t="n">
+        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$56,WBS!$B$5:$B$56,$A8)</f>
         <v>46244</v>
       </c>
-      <c r="E8" s="34" t="n">
-        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$46,WBS!$B$5:$B$46,$A8)</f>
+      <c r="E8" s="36" t="n">
+        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$56,WBS!$B$5:$B$56,$A8)</f>
         <v>46248</v>
       </c>
-      <c r="F8" s="34" t="n">
-        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A8)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A8))</f>
+      <c r="F8" s="36" t="n">
+        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A8)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A8))</f>
         <v>46252</v>
       </c>
-      <c r="G8" s="34" t="n">
-        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A8)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A8))</f>
+      <c r="G8" s="36" t="n">
+        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A8)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A8))</f>
         <v>46252</v>
       </c>
-      <c r="H8" s="35" t="n">
-        <f aca="false">SUMIFS(WBS!$L$5:$L$46,WBS!$B$5:$B$46,$A8)</f>
-        <v>0.0952380952380953</v>
-      </c>
-      <c r="I8" s="36" t="n">
-        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$46,WBS!$B$5:$B$46,$A8)/$H8,0)</f>
+      <c r="H8" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$B$5:$B$56,$A8)</f>
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I8" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$B$5:$B$56,$A8)/$H8,0)</f>
         <v>1</v>
       </c>
-      <c r="J8" s="38" t="n">
+      <c r="J8" s="40" t="n">
         <v>0.06</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="35" t="s">
         <v>90</v>
       </c>
       <c r="B9" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A9)</f>
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A9)</f>
         <v>3</v>
       </c>
       <c r="C9" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A9,WBS!$E$5:$E$46,"Selesai")</f>
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A9,WBS!$E$5:$E$56,"Selesai")</f>
         <v>3</v>
       </c>
-      <c r="D9" s="34" t="n">
-        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$46,WBS!$B$5:$B$46,$A9)</f>
+      <c r="D9" s="36" t="n">
+        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$56,WBS!$B$5:$B$56,$A9)</f>
         <v>46251</v>
       </c>
-      <c r="E9" s="34" t="n">
-        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$46,WBS!$B$5:$B$46,$A9)</f>
+      <c r="E9" s="36" t="n">
+        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$56,WBS!$B$5:$B$56,$A9)</f>
         <v>46255</v>
       </c>
-      <c r="F9" s="34" t="n">
-        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A9)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A9))</f>
+      <c r="F9" s="36" t="n">
+        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A9)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A9))</f>
         <v>46252</v>
       </c>
-      <c r="G9" s="34" t="n">
-        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A9)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A9))</f>
+      <c r="G9" s="36" t="n">
+        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A9)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A9))</f>
         <v>46252</v>
       </c>
-      <c r="H9" s="35" t="n">
-        <f aca="false">SUMIFS(WBS!$L$5:$L$46,WBS!$B$5:$B$46,$A9)</f>
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="I9" s="36" t="n">
-        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$46,WBS!$B$5:$B$46,$A9)/$H9,0)</f>
+      <c r="H9" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$B$5:$B$56,$A9)</f>
+        <v>0.0576923076923077</v>
+      </c>
+      <c r="I9" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$B$5:$B$56,$A9)/$H9,0)</f>
         <v>1</v>
       </c>
-      <c r="J9" s="38" t="n">
+      <c r="J9" s="40" t="n">
         <v>0.02</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="35" t="s">
         <v>100</v>
       </c>
       <c r="B10" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A10)</f>
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A10)</f>
         <v>4</v>
       </c>
       <c r="C10" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A10,WBS!$E$5:$E$46,"Selesai")</f>
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A10,WBS!$E$5:$E$56,"Selesai")</f>
+        <v>4</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$56,WBS!$B$5:$B$56,$A10)</f>
+        <v>46258</v>
+      </c>
+      <c r="E10" s="36" t="n">
+        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$56,WBS!$B$5:$B$56,$A10)</f>
+        <v>46269</v>
+      </c>
+      <c r="F10" s="36" t="n">
+        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A10)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A10))</f>
+        <v>46254</v>
+      </c>
+      <c r="G10" s="36" t="n">
+        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A10)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A10))</f>
+        <v>46270</v>
+      </c>
+      <c r="H10" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$B$5:$B$56,$A10)</f>
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I10" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$B$5:$B$56,$A10)/$H10,0)</f>
+        <v>1</v>
+      </c>
+      <c r="J10" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A11)</f>
+        <v>3</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A11,WBS!$E$5:$E$56,"Selesai")</f>
+        <v>3</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$56,WBS!$B$5:$B$56,$A11)</f>
+        <v>46272</v>
+      </c>
+      <c r="E11" s="36" t="n">
+        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$56,WBS!$B$5:$B$56,$A11)</f>
+        <v>46276</v>
+      </c>
+      <c r="F11" s="36" t="n">
+        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A11)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A11))</f>
+        <v>46270</v>
+      </c>
+      <c r="G11" s="36" t="n">
+        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A11)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A11))</f>
+        <v>46270</v>
+      </c>
+      <c r="H11" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$B$5:$B$56,$A11)</f>
+        <v>0.0576923076923077</v>
+      </c>
+      <c r="I11" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$B$5:$B$56,$A11)/$H11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="J11" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A12)</f>
+        <v>7</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A12,WBS!$E$5:$E$56,"Selesai")</f>
+        <v>6</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$56,WBS!$B$5:$B$56,$A12)</f>
+        <v>46279</v>
+      </c>
+      <c r="E12" s="36" t="n">
+        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$56,WBS!$B$5:$B$56,$A12)</f>
+        <v>46283</v>
+      </c>
+      <c r="F12" s="36" t="n">
+        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A12)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A12))</f>
+        <v>46270</v>
+      </c>
+      <c r="G12" s="36" t="n">
+        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A12)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A12))</f>
+        <v>46270</v>
+      </c>
+      <c r="H12" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$B$5:$B$56,$A12)</f>
+        <v>0.134615384615385</v>
+      </c>
+      <c r="I12" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$B$5:$B$56,$A12)/$H12,0)</f>
+        <v>0.857142857142857</v>
+      </c>
+      <c r="J12" s="40" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A13)</f>
+        <v>4</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A13,WBS!$E$5:$E$56,"Selesai")</f>
         <v>0</v>
       </c>
-      <c r="D10" s="34" t="n">
-        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$46,WBS!$B$5:$B$46,$A10)</f>
-        <v>46258</v>
-      </c>
-      <c r="E10" s="34" t="n">
-        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$46,WBS!$B$5:$B$46,$A10)</f>
-        <v>46269</v>
-      </c>
-      <c r="F10" s="34" t="str">
-        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A10)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A10))</f>
+      <c r="D13" s="36" t="n">
+        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$56,WBS!$B$5:$B$56,$A13)</f>
+        <v>46286</v>
+      </c>
+      <c r="E13" s="36" t="n">
+        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$56,WBS!$B$5:$B$56,$A13)</f>
+        <v>46290</v>
+      </c>
+      <c r="F13" s="36" t="str">
+        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A13)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A13))</f>
         <v>-</v>
       </c>
-      <c r="G10" s="34" t="str">
-        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A10)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A10))</f>
+      <c r="G13" s="36" t="str">
+        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A13)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A13))</f>
         <v>-</v>
       </c>
-      <c r="H10" s="35" t="n">
-        <f aca="false">SUMIFS(WBS!$L$5:$L$46,WBS!$B$5:$B$46,$A10)</f>
-        <v>0.0952380952380953</v>
-      </c>
-      <c r="I10" s="36" t="n">
-        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$46,WBS!$B$5:$B$46,$A10)/$H10,0)</f>
+      <c r="H13" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$B$5:$B$56,$A13)</f>
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I13" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$B$5:$B$56,$A13)/$H13,0)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="38" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A11)</f>
-        <v>3</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A11,WBS!$E$5:$E$46,"Selesai")</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="34" t="n">
-        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$46,WBS!$B$5:$B$46,$A11)</f>
+      <c r="J13" s="40" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A14)</f>
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$B$5:$B$56,$A14,WBS!$E$5:$E$56,"Selesai")</f>
+        <v>9</v>
+      </c>
+      <c r="D14" s="36" t="n">
+        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$56,WBS!$B$5:$B$56,$A14)</f>
+        <v>46270</v>
+      </c>
+      <c r="E14" s="36" t="n">
+        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$56,WBS!$B$5:$B$56,$A14)</f>
         <v>46272</v>
       </c>
-      <c r="E11" s="34" t="n">
-        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$46,WBS!$B$5:$B$46,$A11)</f>
-        <v>46276</v>
-      </c>
-      <c r="F11" s="34" t="str">
-        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A11)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A11))</f>
-        <v>-</v>
-      </c>
-      <c r="G11" s="34" t="str">
-        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A11)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A11))</f>
-        <v>-</v>
-      </c>
-      <c r="H11" s="35" t="n">
-        <f aca="false">SUMIFS(WBS!$L$5:$L$46,WBS!$B$5:$B$46,$A11)</f>
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="I11" s="36" t="n">
-        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$46,WBS!$B$5:$B$46,$A11)/$H11,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A12)</f>
-        <v>7</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A12,WBS!$E$5:$E$46,"Selesai")</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="34" t="n">
-        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$46,WBS!$B$5:$B$46,$A12)</f>
-        <v>46279</v>
-      </c>
-      <c r="E12" s="34" t="n">
-        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$46,WBS!$B$5:$B$46,$A12)</f>
-        <v>46283</v>
-      </c>
-      <c r="F12" s="34" t="str">
-        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A12)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A12))</f>
-        <v>-</v>
-      </c>
-      <c r="G12" s="34" t="str">
-        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A12)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A12))</f>
-        <v>-</v>
-      </c>
-      <c r="H12" s="35" t="n">
-        <f aca="false">SUMIFS(WBS!$L$5:$L$46,WBS!$B$5:$B$46,$A12)</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I12" s="36" t="n">
-        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$46,WBS!$B$5:$B$46,$A12)/$H12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="38" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A13)</f>
-        <v>4</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$B$5:$B$46,$A13,WBS!$E$5:$E$46,"Selesai")</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="34" t="n">
-        <f aca="false">_xlfn.MINIFS(WBS!$F$5:$F$46,WBS!$B$5:$B$46,$A13)</f>
-        <v>46286</v>
-      </c>
-      <c r="E13" s="34" t="n">
-        <f aca="false">_xlfn.MAXIFS(WBS!$G$5:$G$46,WBS!$B$5:$B$46,$A13)</f>
-        <v>46290</v>
-      </c>
-      <c r="F13" s="34" t="str">
-        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A13)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,$A13))</f>
-        <v>-</v>
-      </c>
-      <c r="G13" s="34" t="str">
-        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A13)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$46,WBS!$B$5:$B$46,$A13))</f>
-        <v>-</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <f aca="false">SUMIFS(WBS!$L$5:$L$46,WBS!$B$5:$B$46,$A13)</f>
-        <v>0.0952380952380953</v>
-      </c>
-      <c r="I13" s="36" t="n">
-        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$46,WBS!$B$5:$B$46,$A13)/$H13,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="38" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="B14" s="24" t="n">
-        <f aca="false">SUM(B5:B13)</f>
-        <v>42</v>
-      </c>
-      <c r="C14" s="24" t="n">
-        <f aca="false">SUM(C5:C13)</f>
-        <v>24</v>
-      </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="25" t="n">
-        <f aca="false">SUM(H5:H13)</f>
+      <c r="F14" s="36" t="n">
+        <f aca="false">IF(_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A14)=0,"-",_xlfn.MINIFS(WBS!$I$5:$I$56,WBS!$B$5:$B$56,$A14))</f>
+        <v>46270</v>
+      </c>
+      <c r="G14" s="36" t="n">
+        <f aca="false">IF(_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A14)=0,"-",_xlfn.MAXIFS(WBS!$J$5:$J$56,WBS!$B$5:$B$56,$A14))</f>
+        <v>46270</v>
+      </c>
+      <c r="H14" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$B$5:$B$56,$A14)</f>
+        <v>0.192307692307692</v>
+      </c>
+      <c r="I14" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$B$5:$B$56,$A14)/$H14,0)</f>
+        <v>0.9</v>
+      </c>
+      <c r="J14" s="40" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" s="26" t="n">
+        <f aca="false">SUM(B5:B14)</f>
+        <v>52</v>
+      </c>
+      <c r="C15" s="26" t="n">
+        <f aca="false">SUM(C5:C14)</f>
+        <v>46</v>
+      </c>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="27" t="n">
+        <f aca="false">SUM(H5:H14)</f>
         <v>1</v>
       </c>
-      <c r="I14" s="25" t="n">
-        <f aca="false">SUM(WBS!$N$5:$N$46)</f>
-        <v>0.571428571428572</v>
-      </c>
-      <c r="J14" s="39" t="n">
-        <f aca="false">SUM(J5:J13)</f>
-        <v>12.08</v>
-      </c>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="40" t="s">
-        <v>198</v>
-      </c>
+      <c r="I15" s="27" t="n">
+        <f aca="false">SUM(WBS!$N$5:$N$56)</f>
+        <v>0.884615384615385</v>
+      </c>
+      <c r="J15" s="41" t="n">
+        <f aca="false">SUM(J5:J14)</f>
+        <v>14.95</v>
+      </c>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="B17" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="C17" s="30" t="s">
+      <c r="A17" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D18" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="E18" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="30" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$K$5:$K$46,$A18)</f>
+      <c r="F18" s="32" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$K$5:$K$56,$A19)</f>
         <v>16</v>
       </c>
-      <c r="C18" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$K$5:$K$46,$A18,WBS!$E$5:$E$46,"Selesai")</f>
+      <c r="C19" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$K$5:$K$56,$A19,WBS!$E$5:$E$56,"Selesai")</f>
         <v>16</v>
       </c>
-      <c r="D18" s="35" t="n">
-        <f aca="false">SUMIFS(WBS!$L$5:$L$46,WBS!$K$5:$K$46,$A18)</f>
-        <v>0.380952380952381</v>
-      </c>
-      <c r="E18" s="36" t="n">
-        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$46,WBS!$K$5:$K$46,$A18)/$D18,0)</f>
+      <c r="D19" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$K$5:$K$56,$A19)</f>
+        <v>0.307692307692308</v>
+      </c>
+      <c r="E19" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$K$5:$K$56,$A19)/$D19,0)</f>
         <v>1</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="B19" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$K$5:$K$46,$A19)</f>
+      <c r="F19" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$K$5:$K$56,$A20)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$K$5:$K$46,$A19,WBS!$E$5:$E$46,"Selesai")</f>
-        <v>8</v>
-      </c>
-      <c r="D19" s="35" t="n">
-        <f aca="false">SUMIFS(WBS!$L$5:$L$46,WBS!$K$5:$K$46,$A19)</f>
-        <v>0.238095238095238</v>
-      </c>
-      <c r="E19" s="36" t="n">
-        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$46,WBS!$K$5:$K$46,$A19)/$D19,0)</f>
-        <v>0.8</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="B20" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$K$5:$K$46,$A20)</f>
-        <v>16</v>
-      </c>
       <c r="C20" s="4" t="n">
-        <f aca="false">COUNTIFS(WBS!$K$5:$K$46,$A20,WBS!$E$5:$E$46,"Selesai")</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="35" t="n">
-        <f aca="false">SUMIFS(WBS!$L$5:$L$46,WBS!$K$5:$K$46,$A20)</f>
-        <v>0.380952380952381</v>
-      </c>
-      <c r="E20" s="36" t="n">
-        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$46,WBS!$K$5:$K$46,$A20)/$D20,0)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(WBS!$K$5:$K$56,$A20,WBS!$E$5:$E$56,"Selesai")</f>
+        <v>10</v>
+      </c>
+      <c r="D20" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$K$5:$K$56,$A20)</f>
+        <v>0.192307692307692</v>
+      </c>
+      <c r="E20" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$K$5:$K$56,$A20)/$D20,0)</f>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>206</v>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$K$5:$K$56,$A21)</f>
+        <v>26</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <f aca="false">COUNTIFS(WBS!$K$5:$K$56,$A21,WBS!$E$5:$E$56,"Selesai")</f>
+        <v>20</v>
+      </c>
+      <c r="D21" s="37" t="n">
+        <f aca="false">SUMIFS(WBS!$L$5:$L$56,WBS!$K$5:$K$56,$A21)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="38" t="n">
+        <f aca="false">IFERROR(SUMIFS(WBS!$N$5:$N$56,WBS!$K$5:$K$56,$A21)/$D21,0)</f>
+        <v>0.769230769230769</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -7539,7 +9007,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -7548,212 +9016,244 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="44"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="s">
-        <v>208</v>
+      <c r="A4" s="45" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>210</v>
+      <c r="A5" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>212</v>
+      <c r="A6" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="s">
-        <v>213</v>
-      </c>
-      <c r="B7" s="42" t="s">
-        <v>214</v>
+      <c r="A7" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>216</v>
+      <c r="A8" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41"/>
-      <c r="B9" s="42"/>
+      <c r="A9" s="43"/>
+      <c r="B9" s="44"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="s">
-        <v>217</v>
+      <c r="A10" s="45" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="B11" s="42" t="s">
-        <v>219</v>
+      <c r="A11" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>221</v>
+      <c r="A12" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="41" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="42" t="s">
-        <v>223</v>
+      <c r="A13" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="41" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" s="42" t="s">
-        <v>225</v>
+      <c r="A14" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="41"/>
-      <c r="B15" s="42"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="44"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="43" t="s">
-        <v>226</v>
+      <c r="A16" s="45" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="42" t="s">
-        <v>227</v>
+      <c r="B17" s="44" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>228</v>
+      <c r="A18" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="41" t="s">
-        <v>127</v>
-      </c>
-      <c r="B19" s="42" t="s">
-        <v>229</v>
+      <c r="A19" s="43" t="s">
+        <v>261</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>230</v>
+      <c r="A20" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="44" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="41"/>
-      <c r="B21" s="42"/>
+      <c r="A21" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="44" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="43" t="s">
-        <v>231</v>
-      </c>
+      <c r="A22" s="43"/>
+      <c r="B22" s="44"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="B23" s="42" t="s">
-        <v>233</v>
+      <c r="A23" s="45" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="41" t="s">
-        <v>234</v>
-      </c>
-      <c r="B24" s="42" t="s">
-        <v>235</v>
+      <c r="A24" s="43" t="s">
+        <v>266</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="41" t="s">
-        <v>236</v>
-      </c>
-      <c r="B25" s="42" t="s">
-        <v>237</v>
+      <c r="A25" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="41"/>
-      <c r="B26" s="42"/>
+      <c r="A26" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="B26" s="44" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="43" t="s">
-        <v>238</v>
+        <v>272</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="41" t="s">
-        <v>239</v>
-      </c>
-      <c r="B28" s="42" t="s">
-        <v>240</v>
+      <c r="A28" s="43" t="s">
+        <v>274</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="41" t="s">
-        <v>241</v>
-      </c>
-      <c r="B29" s="42" t="s">
-        <v>242</v>
+      <c r="A29" s="43" t="s">
+        <v>276</v>
+      </c>
+      <c r="B29" s="44" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="B30" s="42" t="s">
-        <v>244</v>
-      </c>
+      <c r="A30" s="43"/>
+      <c r="B30" s="44"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="41" t="s">
-        <v>245</v>
-      </c>
-      <c r="B31" s="42" t="s">
-        <v>246</v>
+      <c r="A31" s="45" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="41" t="s">
-        <v>247</v>
-      </c>
-      <c r="B32" s="42" t="s">
-        <v>248</v>
+      <c r="A32" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="B32" s="44" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="B33" s="44" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="43" t="s">
+        <v>283</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B35" s="44" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="B36" s="44" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
